--- a/core/management/ปัญหางาน NG แยกประเภท.xlsx
+++ b/core/management/ปัญหางาน NG แยกประเภท.xlsx
@@ -4,18 +4,24 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24912" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24910" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="ตัวอย่าง" sheetId="1" state="hidden" r:id="rId2"/>
-    <sheet name="Frame" sheetId="10" r:id="rId3"/>
-    <sheet name="Arm" sheetId="4" r:id="rId4"/>
-    <sheet name="ST" sheetId="11" r:id="rId5"/>
-    <sheet name="CHC" sheetId="12" r:id="rId6"/>
-    <sheet name="RR" sheetId="13" r:id="rId7"/>
-    <sheet name="Loop" sheetId="14" r:id="rId8"/>
+    <sheet name="Cleancing data" sheetId="16" r:id="rId3"/>
+    <sheet name="DeectByCategory" sheetId="15" r:id="rId4"/>
+    <sheet name="Frame" sheetId="10" r:id="rId5"/>
+    <sheet name="Arm" sheetId="4" r:id="rId6"/>
+    <sheet name="ST" sheetId="11" r:id="rId7"/>
+    <sheet name="CHC" sheetId="12" r:id="rId8"/>
+    <sheet name="RR" sheetId="13" r:id="rId9"/>
+    <sheet name="Loop" sheetId="14" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cleancing data'!$B$1:$C$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DeectByCategory!$A$1:$D$142</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="382">
   <si>
     <t>Scrap</t>
   </si>
@@ -868,17 +874,332 @@
   </si>
   <si>
     <t>Test ทำลาย</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Defect mode</t>
+  </si>
+  <si>
+    <t>Side frame</t>
+  </si>
+  <si>
+    <t>ภาษาไทย</t>
+  </si>
+  <si>
+    <t>Lower arm</t>
+  </si>
+  <si>
+    <t>Seattrack</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t>Round recline</t>
+  </si>
+  <si>
+    <t>Loop handle</t>
+  </si>
+  <si>
+    <t>Spec NG</t>
+  </si>
+  <si>
+    <t>TESTทำลาย</t>
+  </si>
+  <si>
+    <t>BREAK TEST</t>
+  </si>
+  <si>
+    <t>Defect mode(EN)</t>
+  </si>
+  <si>
+    <t>Defect mode(TH)</t>
+  </si>
+  <si>
+    <t>Bending deform</t>
+  </si>
+  <si>
+    <t>การดัดเสียรูป</t>
+  </si>
+  <si>
+    <t>End lock angle NG</t>
+  </si>
+  <si>
+    <t>Bush deform</t>
+  </si>
+  <si>
+    <t>Bolt Spot burr</t>
+  </si>
+  <si>
+    <t>Bolt Spot tilt</t>
+  </si>
+  <si>
+    <t>TEST เครื่องจักร</t>
+  </si>
+  <si>
+    <t>Cut ring</t>
+  </si>
+  <si>
+    <t>Bolt เกลียวเสียรูป</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bkt Fr Gap </t>
+  </si>
+  <si>
+    <t>Bkt Rr Gap</t>
+  </si>
+  <si>
+    <t>Bolt GAP</t>
+  </si>
+  <si>
+    <t>Bolt Thread flaw</t>
+  </si>
+  <si>
+    <t>Bolt spot in-complete.</t>
+  </si>
+  <si>
+    <t>Bolt Spotเป็นครีบ</t>
+  </si>
+  <si>
+    <t>Defect Code</t>
+  </si>
+  <si>
+    <t>Lwr Rail Spec NG</t>
+  </si>
+  <si>
+    <t>Upr Rail Spec NG</t>
+  </si>
+  <si>
+    <t>Sliding Torque NG</t>
+  </si>
+  <si>
+    <t>Scratch</t>
+  </si>
+  <si>
+    <t>flaw</t>
+  </si>
+  <si>
+    <t>dent</t>
+  </si>
+  <si>
+    <t>Burr</t>
+  </si>
+  <si>
+    <t>Injection incomplete</t>
+  </si>
+  <si>
+    <t>Slit NG</t>
+  </si>
+  <si>
+    <t>Scrap marks</t>
+  </si>
+  <si>
+    <t>Spring deform</t>
+  </si>
+  <si>
+    <t>Wrong part assembly</t>
+  </si>
+  <si>
+    <t>Lock angle NG</t>
+  </si>
+  <si>
+    <t>W-way loose NG</t>
+  </si>
+  <si>
+    <t>L Gata NG</t>
+  </si>
+  <si>
+    <t>W Gata NG</t>
+  </si>
+  <si>
+    <t>Crack</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Deform</t>
+  </si>
+  <si>
+    <t>Stain</t>
+  </si>
+  <si>
+    <t>ชิ้นงานเป็นสนิม</t>
+  </si>
+  <si>
+    <t>ชิ้นงานเสียรูป</t>
+  </si>
+  <si>
+    <t>ชิ้นงานเป็นคราบ</t>
+  </si>
+  <si>
+    <t>รอยจิก รอยยุบ</t>
+  </si>
+  <si>
+    <t>Wrinkles</t>
+  </si>
+  <si>
+    <t>Raised</t>
+  </si>
+  <si>
+    <t>burn marks</t>
+  </si>
+  <si>
+    <t>Pin deform</t>
+  </si>
+  <si>
+    <t>Pin spot NG</t>
+  </si>
+  <si>
+    <t>องศาล็อคไม่ตรงตำแหน่ง</t>
+  </si>
+  <si>
+    <t>Loose</t>
+  </si>
+  <si>
+    <t>หลวมคลอน</t>
+  </si>
+  <si>
+    <t>Skip Process</t>
+  </si>
+  <si>
+    <t>ข้ามกระบวนการ</t>
+  </si>
+  <si>
+    <t>Dirty</t>
+  </si>
+  <si>
+    <t>สกปรก</t>
+  </si>
+  <si>
+    <t>ตัดRing</t>
+  </si>
+  <si>
+    <t>Welding bead pit</t>
+  </si>
+  <si>
+    <t>Welding bead incomplete</t>
+  </si>
+  <si>
+    <t>Welding bead misalignment</t>
+  </si>
+  <si>
+    <t>Welding bead burn through</t>
+  </si>
+  <si>
+    <t>White stain</t>
+  </si>
+  <si>
+    <t>ขนาดLwr Railไม่เป็นไปตามข้อกำหนด</t>
+  </si>
+  <si>
+    <t>ขนาดUpr Railไม่เป็นไปตามข้อกำหนด</t>
+  </si>
+  <si>
+    <t>Guide broken</t>
+  </si>
+  <si>
+    <t>Guide tears</t>
+  </si>
+  <si>
+    <t>Guideฉีก</t>
+  </si>
+  <si>
+    <t>Guideแตก</t>
+  </si>
+  <si>
+    <t>เศษSpecterติดเกลียวNut</t>
+  </si>
+  <si>
+    <t>Used Spring</t>
+  </si>
+  <si>
+    <t>สปริงใช้แล้ว</t>
+  </si>
+  <si>
+    <t>Spatter on Nut thread</t>
+  </si>
+  <si>
+    <t>Vibration incomplete</t>
+  </si>
+  <si>
+    <t>GAP</t>
+  </si>
+  <si>
+    <t>QC TEST</t>
+  </si>
+  <si>
+    <t>ค่า Slide Hight</t>
+  </si>
+  <si>
+    <t>Revet deform</t>
+  </si>
+  <si>
+    <t>NGเนื่องจากไม่พบข้อมูล</t>
+  </si>
+  <si>
+    <t>ขนาดชิ้นงานไม่เป็นไปตามข้อกำหนด</t>
+  </si>
+  <si>
+    <t>Paint granules</t>
+  </si>
+  <si>
+    <t>Paint stains</t>
+  </si>
+  <si>
+    <t>Cover interference</t>
+  </si>
+  <si>
+    <t>Protector interference</t>
+  </si>
+  <si>
+    <t>อันเดียวกันมั้ย</t>
+  </si>
+  <si>
+    <t>องศาส่วนปลายNG</t>
+  </si>
+  <si>
+    <t>Slide smooth hight</t>
+  </si>
+  <si>
+    <t>Slide smooth Low</t>
+  </si>
+  <si>
+    <t>Slide smooth</t>
+  </si>
+  <si>
+    <t>Spot Patch is a gap.</t>
+  </si>
+  <si>
+    <t>Spring is wrong part number.</t>
+  </si>
+  <si>
+    <t>Spring detached</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Can not Assembly</t>
+  </si>
+  <si>
+    <t>Guide plat's ditch dimension out spec</t>
+  </si>
+  <si>
+    <t>Swing torque NG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -886,7 +1207,7 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -895,8 +1216,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -933,8 +1267,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -994,13 +1352,133 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1030,6 +1508,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1045,12 +1546,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1495,9 +1991,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F195"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.4140625" customWidth="1"/>
     <col min="3" max="6" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1519,7 +2015,7 @@
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1536,7 +2032,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1551,7 +2047,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="14"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1566,7 +2062,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="14"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1581,7 +2077,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1596,7 +2092,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="14"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1611,7 +2107,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="14"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1626,7 +2122,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="14"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1641,7 +2137,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="14"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1656,7 +2152,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="14"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1671,7 +2167,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="14"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +2182,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="14"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1701,7 +2197,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="14"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1716,7 +2212,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="14"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1731,7 +2227,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="14"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1746,7 +2242,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="14"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1761,7 +2257,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1776,7 +2272,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1791,7 +2287,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1806,7 +2302,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1821,7 +2317,7 @@
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
@@ -1836,7 +2332,7 @@
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="15"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="1" t="s">
         <v>26</v>
       </c>
@@ -1851,7 +2347,7 @@
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="34" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1868,7 +2364,7 @@
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="14"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1883,7 +2379,7 @@
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="14"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1898,7 +2394,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="14"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="1" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +2409,7 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="14"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
@@ -1928,7 +2424,7 @@
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="14"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
@@ -1943,7 +2439,7 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="14"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1958,7 +2454,7 @@
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="14"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
@@ -1973,7 +2469,7 @@
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="14"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
@@ -1988,7 +2484,7 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="14"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="1" t="s">
         <v>31</v>
       </c>
@@ -2003,7 +2499,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="14"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
@@ -2018,7 +2514,7 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="14"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="1" t="s">
         <v>14</v>
       </c>
@@ -2033,7 +2529,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="14"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
@@ -2048,7 +2544,7 @@
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="14"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
@@ -2063,7 +2559,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="14"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2078,7 +2574,7 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="14"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
@@ -2093,7 +2589,7 @@
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="14"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
@@ -2108,7 +2604,7 @@
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="14"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
@@ -2123,7 +2619,7 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="14"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="1" t="s">
         <v>34</v>
       </c>
@@ -2138,7 +2634,7 @@
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="14"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
@@ -2153,7 +2649,7 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="14"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="1" t="s">
         <v>25</v>
       </c>
@@ -2168,7 +2664,7 @@
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="15"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
@@ -2183,7 +2679,7 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="34" t="s">
         <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -2200,7 +2696,7 @@
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="14"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="1" t="s">
         <v>38</v>
       </c>
@@ -2215,7 +2711,7 @@
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="14"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="1" t="s">
         <v>39</v>
       </c>
@@ -2230,7 +2726,7 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="14"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
@@ -2245,7 +2741,7 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="14"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
@@ -2260,7 +2756,7 @@
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="14"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="1" t="s">
         <v>28</v>
       </c>
@@ -2275,7 +2771,7 @@
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="14"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="1" t="s">
         <v>0</v>
       </c>
@@ -2290,7 +2786,7 @@
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="14"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,7 +2801,7 @@
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="14"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
@@ -2320,7 +2816,7 @@
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="14"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
@@ -2335,7 +2831,7 @@
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="14"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="1" t="s">
         <v>13</v>
       </c>
@@ -2350,7 +2846,7 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="14"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="1" t="s">
         <v>40</v>
       </c>
@@ -2365,7 +2861,7 @@
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="14"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="1" t="s">
         <v>31</v>
       </c>
@@ -2380,7 +2876,7 @@
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="14"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
@@ -2395,7 +2891,7 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="14"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="1" t="s">
         <v>14</v>
       </c>
@@ -2410,7 +2906,7 @@
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="14"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
@@ -2425,7 +2921,7 @@
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="14"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="1" t="s">
         <v>16</v>
       </c>
@@ -2440,7 +2936,7 @@
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="14"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
@@ -2455,7 +2951,7 @@
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="14"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="1" t="s">
         <v>18</v>
       </c>
@@ -2470,7 +2966,7 @@
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="14"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="1" t="s">
         <v>12</v>
       </c>
@@ -2485,7 +2981,7 @@
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="14"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
@@ -2500,7 +2996,7 @@
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="14"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
@@ -2515,7 +3011,7 @@
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="14"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
@@ -2530,7 +3026,7 @@
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="14"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
@@ -2545,7 +3041,7 @@
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="14"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
@@ -2560,7 +3056,7 @@
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="14"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,7 +3071,7 @@
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="14"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="1" t="s">
         <v>34</v>
       </c>
@@ -2590,7 +3086,7 @@
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="14"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="1" t="s">
         <v>35</v>
       </c>
@@ -2605,7 +3101,7 @@
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="14"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="1" t="s">
         <v>41</v>
       </c>
@@ -2620,7 +3116,7 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="14"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="1" t="s">
         <v>13</v>
       </c>
@@ -2635,7 +3131,7 @@
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="14"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="1" t="s">
         <v>25</v>
       </c>
@@ -2650,7 +3146,7 @@
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="15"/>
+      <c r="B78" s="36"/>
       <c r="C78" s="1" t="s">
         <v>26</v>
       </c>
@@ -2665,7 +3161,7 @@
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="34" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -2682,7 +3178,7 @@
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="14"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="1" t="s">
         <v>0</v>
       </c>
@@ -2697,7 +3193,7 @@
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="14"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
@@ -2712,7 +3208,7 @@
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="14"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="1" t="s">
         <v>30</v>
       </c>
@@ -2727,7 +3223,7 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="14"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
@@ -2742,7 +3238,7 @@
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="14"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
@@ -2757,7 +3253,7 @@
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="14"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="1" t="s">
         <v>13</v>
       </c>
@@ -2772,7 +3268,7 @@
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="14"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="1" t="s">
         <v>31</v>
       </c>
@@ -2787,7 +3283,7 @@
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="14"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="2" t="s">
         <v>52</v>
       </c>
@@ -2802,7 +3298,7 @@
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="14"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="1" t="s">
         <v>14</v>
       </c>
@@ -2817,7 +3313,7 @@
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="14"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="1" t="s">
         <v>15</v>
       </c>
@@ -2832,7 +3328,7 @@
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="14"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="1" t="s">
         <v>18</v>
       </c>
@@ -2847,7 +3343,7 @@
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="14"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="1" t="s">
         <v>12</v>
       </c>
@@ -2862,7 +3358,7 @@
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="14"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="1" t="s">
         <v>32</v>
       </c>
@@ -2877,7 +3373,7 @@
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="14"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="1" t="s">
         <v>33</v>
       </c>
@@ -2889,7 +3385,7 @@
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="14"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="1" t="s">
         <v>19</v>
       </c>
@@ -2901,7 +3397,7 @@
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="14"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
@@ -2913,7 +3409,7 @@
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B96" s="14"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="1" t="s">
         <v>20</v>
       </c>
@@ -2925,7 +3421,7 @@
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B97" s="14"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="1" t="s">
         <v>34</v>
       </c>
@@ -2937,7 +3433,7 @@
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="14"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="1" t="s">
         <v>27</v>
       </c>
@@ -2949,7 +3445,7 @@
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="14"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
@@ -2961,7 +3457,7 @@
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="14"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="1" t="s">
         <v>44</v>
       </c>
@@ -2973,7 +3469,7 @@
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="14"/>
+      <c r="B101" s="35"/>
       <c r="C101" s="1" t="s">
         <v>45</v>
       </c>
@@ -2985,7 +3481,7 @@
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="14"/>
+      <c r="B102" s="35"/>
       <c r="C102" s="1" t="s">
         <v>47</v>
       </c>
@@ -2997,7 +3493,7 @@
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="14"/>
+      <c r="B103" s="35"/>
       <c r="C103" s="1" t="s">
         <v>46</v>
       </c>
@@ -3009,7 +3505,7 @@
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="14"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="1" t="s">
         <v>25</v>
       </c>
@@ -3021,7 +3517,7 @@
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="15"/>
+      <c r="B105" s="36"/>
       <c r="C105" s="1" t="s">
         <v>26</v>
       </c>
@@ -3033,7 +3529,7 @@
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="34" t="s">
         <v>48</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -3047,7 +3543,7 @@
       </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="14"/>
+      <c r="B107" s="35"/>
       <c r="C107" s="1" t="s">
         <v>27</v>
       </c>
@@ -3059,7 +3555,7 @@
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="14"/>
+      <c r="B108" s="35"/>
       <c r="C108" s="1" t="s">
         <v>28</v>
       </c>
@@ -3071,7 +3567,7 @@
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="14"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="1" t="s">
         <v>0</v>
       </c>
@@ -3083,7 +3579,7 @@
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="14"/>
+      <c r="B110" s="35"/>
       <c r="C110" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,7 +3591,7 @@
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="14"/>
+      <c r="B111" s="35"/>
       <c r="C111" s="1" t="s">
         <v>30</v>
       </c>
@@ -3107,7 +3603,7 @@
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="14"/>
+      <c r="B112" s="35"/>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
@@ -3119,7 +3615,7 @@
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="14"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="1" t="s">
         <v>12</v>
       </c>
@@ -3131,7 +3627,7 @@
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="14"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="1" t="s">
         <v>13</v>
       </c>
@@ -3143,7 +3639,7 @@
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="14"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="1" t="s">
         <v>31</v>
       </c>
@@ -3155,7 +3651,7 @@
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="14"/>
+      <c r="B116" s="35"/>
       <c r="C116" s="2" t="s">
         <v>52</v>
       </c>
@@ -3167,7 +3663,7 @@
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="14"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="1" t="s">
         <v>14</v>
       </c>
@@ -3179,7 +3675,7 @@
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="14"/>
+      <c r="B118" s="35"/>
       <c r="C118" s="1" t="s">
         <v>15</v>
       </c>
@@ -3191,7 +3687,7 @@
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="14"/>
+      <c r="B119" s="35"/>
       <c r="C119" s="1" t="s">
         <v>16</v>
       </c>
@@ -3203,7 +3699,7 @@
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B120" s="14"/>
+      <c r="B120" s="35"/>
       <c r="C120" s="1" t="s">
         <v>18</v>
       </c>
@@ -3215,7 +3711,7 @@
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B121" s="14"/>
+      <c r="B121" s="35"/>
       <c r="C121" s="1" t="s">
         <v>12</v>
       </c>
@@ -3227,7 +3723,7 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="14"/>
+      <c r="B122" s="35"/>
       <c r="C122" s="1" t="s">
         <v>32</v>
       </c>
@@ -3239,7 +3735,7 @@
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="14"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="1" t="s">
         <v>33</v>
       </c>
@@ -3251,7 +3747,7 @@
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="14"/>
+      <c r="B124" s="35"/>
       <c r="C124" s="1" t="s">
         <v>19</v>
       </c>
@@ -3263,7 +3759,7 @@
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B125" s="14"/>
+      <c r="B125" s="35"/>
       <c r="C125" s="1" t="s">
         <v>10</v>
       </c>
@@ -3275,7 +3771,7 @@
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="14"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
@@ -3287,7 +3783,7 @@
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="14"/>
+      <c r="B127" s="35"/>
       <c r="C127" s="1" t="s">
         <v>20</v>
       </c>
@@ -3299,7 +3795,7 @@
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B128" s="14"/>
+      <c r="B128" s="35"/>
       <c r="C128" s="1" t="s">
         <v>34</v>
       </c>
@@ -3311,7 +3807,7 @@
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B129" s="14"/>
+      <c r="B129" s="35"/>
       <c r="C129" s="1" t="s">
         <v>35</v>
       </c>
@@ -3323,7 +3819,7 @@
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B130" s="14"/>
+      <c r="B130" s="35"/>
       <c r="C130" s="1" t="s">
         <v>25</v>
       </c>
@@ -3335,7 +3831,7 @@
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B131" s="15"/>
+      <c r="B131" s="36"/>
       <c r="C131" s="1" t="s">
         <v>26</v>
       </c>
@@ -3347,7 +3843,7 @@
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="34" t="s">
         <v>49</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -3361,7 +3857,7 @@
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="14"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="1" t="s">
         <v>50</v>
       </c>
@@ -3373,7 +3869,7 @@
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="14"/>
+      <c r="B134" s="35"/>
       <c r="C134" s="1" t="s">
         <v>51</v>
       </c>
@@ -3385,7 +3881,7 @@
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="14"/>
+      <c r="B135" s="35"/>
       <c r="C135" s="1" t="s">
         <v>52</v>
       </c>
@@ -3397,7 +3893,7 @@
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="14"/>
+      <c r="B136" s="35"/>
       <c r="C136" s="1" t="s">
         <v>31</v>
       </c>
@@ -3409,7 +3905,7 @@
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="14"/>
+      <c r="B137" s="35"/>
       <c r="C137" s="1" t="s">
         <v>53</v>
       </c>
@@ -3421,7 +3917,7 @@
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="14"/>
+      <c r="B138" s="35"/>
       <c r="C138" s="1" t="s">
         <v>54</v>
       </c>
@@ -3433,7 +3929,7 @@
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B139" s="14"/>
+      <c r="B139" s="35"/>
       <c r="C139" s="1" t="s">
         <v>55</v>
       </c>
@@ -3445,7 +3941,7 @@
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B140" s="14"/>
+      <c r="B140" s="35"/>
       <c r="C140" s="1" t="s">
         <v>24</v>
       </c>
@@ -3457,7 +3953,7 @@
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="14"/>
+      <c r="B141" s="35"/>
       <c r="C141" s="1" t="s">
         <v>15</v>
       </c>
@@ -3469,7 +3965,7 @@
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="14"/>
+      <c r="B142" s="35"/>
       <c r="C142" s="1" t="s">
         <v>16</v>
       </c>
@@ -3481,7 +3977,7 @@
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B143" s="14"/>
+      <c r="B143" s="35"/>
       <c r="C143" s="1" t="s">
         <v>17</v>
       </c>
@@ -3493,7 +3989,7 @@
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B144" s="14"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="1" t="s">
         <v>18</v>
       </c>
@@ -3505,7 +4001,7 @@
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B145" s="14"/>
+      <c r="B145" s="35"/>
       <c r="C145" s="1" t="s">
         <v>12</v>
       </c>
@@ -3517,7 +4013,7 @@
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B146" s="14"/>
+      <c r="B146" s="35"/>
       <c r="C146" s="1" t="s">
         <v>20</v>
       </c>
@@ -3529,7 +4025,7 @@
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B147" s="14"/>
+      <c r="B147" s="35"/>
       <c r="C147" s="1" t="s">
         <v>32</v>
       </c>
@@ -3541,7 +4037,7 @@
       </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B148" s="14"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="1" t="s">
         <v>10</v>
       </c>
@@ -3553,7 +4049,7 @@
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B149" s="14"/>
+      <c r="B149" s="35"/>
       <c r="C149" s="1" t="s">
         <v>56</v>
       </c>
@@ -3565,7 +4061,7 @@
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B150" s="14"/>
+      <c r="B150" s="35"/>
       <c r="C150" s="1" t="s">
         <v>25</v>
       </c>
@@ -3577,7 +4073,7 @@
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B151" s="15"/>
+      <c r="B151" s="36"/>
       <c r="C151" s="1" t="s">
         <v>26</v>
       </c>
@@ -3589,7 +4085,7 @@
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="34" t="s">
         <v>57</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -3603,7 +4099,7 @@
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B153" s="14"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="1" t="s">
         <v>50</v>
       </c>
@@ -3615,7 +4111,7 @@
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B154" s="14"/>
+      <c r="B154" s="35"/>
       <c r="C154" s="1" t="s">
         <v>51</v>
       </c>
@@ -3627,7 +4123,7 @@
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B155" s="14"/>
+      <c r="B155" s="35"/>
       <c r="C155" s="1" t="s">
         <v>52</v>
       </c>
@@ -3639,7 +4135,7 @@
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B156" s="14"/>
+      <c r="B156" s="35"/>
       <c r="C156" s="1" t="s">
         <v>31</v>
       </c>
@@ -3651,7 +4147,7 @@
       </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B157" s="14"/>
+      <c r="B157" s="35"/>
       <c r="C157" s="1" t="s">
         <v>53</v>
       </c>
@@ -3663,7 +4159,7 @@
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B158" s="14"/>
+      <c r="B158" s="35"/>
       <c r="C158" s="1" t="s">
         <v>54</v>
       </c>
@@ -3675,7 +4171,7 @@
       </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B159" s="14"/>
+      <c r="B159" s="35"/>
       <c r="C159" s="1" t="s">
         <v>55</v>
       </c>
@@ -3687,7 +4183,7 @@
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B160" s="14"/>
+      <c r="B160" s="35"/>
       <c r="C160" s="1" t="s">
         <v>24</v>
       </c>
@@ -3699,7 +4195,7 @@
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B161" s="14"/>
+      <c r="B161" s="35"/>
       <c r="C161" s="1" t="s">
         <v>15</v>
       </c>
@@ -3711,7 +4207,7 @@
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B162" s="14"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="1" t="s">
         <v>16</v>
       </c>
@@ -3723,7 +4219,7 @@
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B163" s="14"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="1" t="s">
         <v>17</v>
       </c>
@@ -3735,7 +4231,7 @@
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B164" s="14"/>
+      <c r="B164" s="35"/>
       <c r="C164" s="1" t="s">
         <v>18</v>
       </c>
@@ -3747,7 +4243,7 @@
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B165" s="14"/>
+      <c r="B165" s="35"/>
       <c r="C165" s="1" t="s">
         <v>12</v>
       </c>
@@ -3759,7 +4255,7 @@
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B166" s="14"/>
+      <c r="B166" s="35"/>
       <c r="C166" s="1" t="s">
         <v>20</v>
       </c>
@@ -3771,7 +4267,7 @@
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B167" s="14"/>
+      <c r="B167" s="35"/>
       <c r="C167" s="1" t="s">
         <v>32</v>
       </c>
@@ -3783,7 +4279,7 @@
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B168" s="14"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="1" t="s">
         <v>10</v>
       </c>
@@ -3795,7 +4291,7 @@
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B169" s="14"/>
+      <c r="B169" s="35"/>
       <c r="C169" s="1" t="s">
         <v>56</v>
       </c>
@@ -3807,7 +4303,7 @@
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B170" s="14"/>
+      <c r="B170" s="35"/>
       <c r="C170" s="1" t="s">
         <v>25</v>
       </c>
@@ -3819,7 +4315,7 @@
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B171" s="15"/>
+      <c r="B171" s="36"/>
       <c r="C171" s="1" t="s">
         <v>26</v>
       </c>
@@ -3831,7 +4327,7 @@
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="34" t="s">
         <v>58</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -3845,7 +4341,7 @@
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B173" s="14"/>
+      <c r="B173" s="35"/>
       <c r="C173" s="1" t="s">
         <v>60</v>
       </c>
@@ -3857,7 +4353,7 @@
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B174" s="14"/>
+      <c r="B174" s="35"/>
       <c r="C174" s="1" t="s">
         <v>61</v>
       </c>
@@ -3869,7 +4365,7 @@
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B175" s="14"/>
+      <c r="B175" s="35"/>
       <c r="C175" s="1" t="s">
         <v>32</v>
       </c>
@@ -3881,7 +4377,7 @@
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B176" s="14"/>
+      <c r="B176" s="35"/>
       <c r="C176" s="1" t="s">
         <v>62</v>
       </c>
@@ -3893,7 +4389,7 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B177" s="14"/>
+      <c r="B177" s="35"/>
       <c r="C177" s="1" t="s">
         <v>63</v>
       </c>
@@ -3905,7 +4401,7 @@
       </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B178" s="14"/>
+      <c r="B178" s="35"/>
       <c r="C178" s="1" t="s">
         <v>64</v>
       </c>
@@ -3917,7 +4413,7 @@
       </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B179" s="14"/>
+      <c r="B179" s="35"/>
       <c r="C179" s="1" t="s">
         <v>65</v>
       </c>
@@ -3929,7 +4425,7 @@
       </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B180" s="14"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="1" t="s">
         <v>66</v>
       </c>
@@ -3941,7 +4437,7 @@
       </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B181" s="14"/>
+      <c r="B181" s="35"/>
       <c r="C181" s="1" t="s">
         <v>67</v>
       </c>
@@ -3953,7 +4449,7 @@
       </c>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B182" s="14"/>
+      <c r="B182" s="35"/>
       <c r="C182" s="1" t="s">
         <v>68</v>
       </c>
@@ -3965,7 +4461,7 @@
       </c>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B183" s="14"/>
+      <c r="B183" s="35"/>
       <c r="C183" s="1" t="s">
         <v>69</v>
       </c>
@@ -3977,7 +4473,7 @@
       </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B184" s="14"/>
+      <c r="B184" s="35"/>
       <c r="C184" s="1" t="s">
         <v>10</v>
       </c>
@@ -3989,7 +4485,7 @@
       </c>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B185" s="14"/>
+      <c r="B185" s="35"/>
       <c r="C185" s="1" t="s">
         <v>70</v>
       </c>
@@ -4001,7 +4497,7 @@
       </c>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B186" s="14"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="1" t="s">
         <v>71</v>
       </c>
@@ -4013,7 +4509,7 @@
       </c>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B187" s="14"/>
+      <c r="B187" s="35"/>
       <c r="C187" s="1" t="s">
         <v>72</v>
       </c>
@@ -4025,7 +4521,7 @@
       </c>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B188" s="14"/>
+      <c r="B188" s="35"/>
       <c r="C188" s="1" t="s">
         <v>34</v>
       </c>
@@ -4037,7 +4533,7 @@
       </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B189" s="14"/>
+      <c r="B189" s="35"/>
       <c r="C189" s="1" t="s">
         <v>12</v>
       </c>
@@ -4049,7 +4545,7 @@
       </c>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B190" s="14"/>
+      <c r="B190" s="35"/>
       <c r="C190" s="1" t="s">
         <v>73</v>
       </c>
@@ -4061,7 +4557,7 @@
       </c>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B191" s="14"/>
+      <c r="B191" s="35"/>
       <c r="C191" s="1" t="s">
         <v>74</v>
       </c>
@@ -4073,7 +4569,7 @@
       </c>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B192" s="14"/>
+      <c r="B192" s="35"/>
       <c r="C192" s="1" t="s">
         <v>75</v>
       </c>
@@ -4085,7 +4581,7 @@
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B193" s="14"/>
+      <c r="B193" s="35"/>
       <c r="C193" s="1" t="s">
         <v>76</v>
       </c>
@@ -4097,7 +4593,7 @@
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B194" s="14"/>
+      <c r="B194" s="35"/>
       <c r="C194" s="1" t="s">
         <v>77</v>
       </c>
@@ -4109,7 +4605,7 @@
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B195" s="15"/>
+      <c r="B195" s="36"/>
       <c r="C195" s="1" t="s">
         <v>78</v>
       </c>
@@ -4135,12 +4631,711 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:E193"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.4140625" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="38"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="7">
+        <v>4</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="7">
+        <v>6</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="7">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="7">
+        <v>9</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="7">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="7">
+        <v>12</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="7">
+        <v>13</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="5"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="5"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="5"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="5"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="5"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="5"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="5"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="5"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="5"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="5"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="5"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="5"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="5"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="5"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" s="5"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="5"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B62" s="5"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B63" s="5"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B64" s="5"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B65" s="5"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B66" s="5"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B67" s="5"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B68" s="5"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B69" s="5"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B70" s="5"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B71" s="5"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B72" s="5"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B73" s="5"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74" s="5"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75" s="5"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B76" s="5"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B77" s="5"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B78" s="5"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B79" s="5"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B80" s="5"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="5"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="5"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B83" s="5"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B84" s="5"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B85" s="5"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B86" s="5"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B87" s="5"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B88" s="5"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B89" s="5"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B90" s="5"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B91" s="5"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B92" s="5"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B93" s="5"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B94" s="6"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B95" s="6"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B96" s="6"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B97" s="6"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B98" s="6"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B99" s="6"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B100" s="6"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B101" s="6"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B102" s="6"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B103" s="6"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B104" s="6"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B105" s="6"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B106" s="6"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B107" s="6"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B108" s="6"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B109" s="6"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B110" s="6"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B111" s="6"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B112" s="6"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B113" s="6"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B114" s="6"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B115" s="6"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B116" s="6"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B117" s="6"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B118" s="6"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B119" s="6"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B120" s="6"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B121" s="6"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B122" s="6"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B123" s="6"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B124" s="6"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B125" s="6"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B126" s="6"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B127" s="6"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B128" s="6"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B129" s="6"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B130" s="6"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B131" s="6"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B132" s="6"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B133" s="6"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B134" s="6"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B135" s="6"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B136" s="6"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B137" s="6"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B138" s="6"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B139" s="6"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B140" s="6"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B141" s="6"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B142" s="6"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B143" s="6"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B144" s="6"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="6"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="6"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B147" s="6"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B148" s="6"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B149" s="6"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B150" s="6"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B151" s="6"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B152" s="6"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B153" s="6"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B154" s="6"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B155" s="6"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B156" s="6"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B157" s="6"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B158" s="6"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B159" s="6"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B160" s="6"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B161" s="6"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B162" s="6"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B163" s="6"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B164" s="6"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B165" s="6"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B166" s="6"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B167" s="6"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B168" s="6"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B169" s="6"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B170" s="6"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B171" s="6"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B172" s="6"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B173" s="6"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B174" s="6"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B175" s="6"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B176" s="6"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B177" s="6"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B178" s="6"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B179" s="6"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B180" s="6"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B181" s="6"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B182" s="6"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B183" s="6"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B184" s="6"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B185" s="6"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B186" s="6"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B187" s="6"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B188" s="6"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B189" s="6"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="6"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B191" s="6"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B192" s="6"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3:C15">
+    <cfRule type="duplicateValues" dxfId="3" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C17">
+    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:C21">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C195"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.4140625" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4153,7 +5348,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4161,133 +5356,133 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="14"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="14"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="14"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="14"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="14"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="14"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="14"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="14"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="14"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="14"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="14"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="14"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="14"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="14"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="14"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="14"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="15"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="34" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -4295,133 +5490,133 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="14"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="14"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="14"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="14"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="14"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="14"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="14"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="14"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="14"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="14"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="14"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" s="14"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="14"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B39" s="14"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" s="14"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B41" s="14"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B42" s="14"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B43" s="14"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" s="14"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B45" s="14"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B46" s="15"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="34" t="s">
         <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -4429,193 +5624,193 @@
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B48" s="14"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="14"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" s="14"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B51" s="14"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B52" s="14"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B53" s="14"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B54" s="14"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B55" s="14"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="14"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B57" s="14"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B58" s="14"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="14"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B60" s="14"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B61" s="14"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B62" s="14"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="14"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B64" s="14"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B65" s="14"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B66" s="14"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B67" s="14"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B68" s="14"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B69" s="14"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B70" s="14"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B71" s="14"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B72" s="14"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B73" s="14"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B74" s="14"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B75" s="14"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B76" s="14"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B77" s="14"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B78" s="15"/>
+      <c r="B78" s="36"/>
       <c r="C78" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="34" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -4623,163 +5818,163 @@
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B80" s="14"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B81" s="14"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B82" s="14"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B83" s="14"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84" s="14"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B85" s="14"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B86" s="14"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B87" s="14"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B88" s="14"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B89" s="14"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B90" s="14"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B91" s="14"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B92" s="14"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B93" s="14"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B94" s="14"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" s="14"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B96" s="14"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" s="14"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98" s="14"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99" s="14"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="14"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B101" s="14"/>
+      <c r="B101" s="35"/>
       <c r="C101" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B102" s="14"/>
+      <c r="B102" s="35"/>
       <c r="C102" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B103" s="14"/>
+      <c r="B103" s="35"/>
       <c r="C103" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B104" s="14"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B105" s="15"/>
+      <c r="B105" s="36"/>
       <c r="C105" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="34" t="s">
         <v>48</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -4787,157 +5982,157 @@
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B107" s="14"/>
+      <c r="B107" s="35"/>
       <c r="C107" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B108" s="14"/>
+      <c r="B108" s="35"/>
       <c r="C108" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B109" s="14"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B110" s="14"/>
+      <c r="B110" s="35"/>
       <c r="C110" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B111" s="14"/>
+      <c r="B111" s="35"/>
       <c r="C111" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B112" s="14"/>
+      <c r="B112" s="35"/>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="14"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B114" s="14"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B115" s="14"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B116" s="14"/>
+      <c r="B116" s="35"/>
       <c r="C116" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B117" s="14"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B118" s="14"/>
+      <c r="B118" s="35"/>
       <c r="C118" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B119" s="14"/>
+      <c r="B119" s="35"/>
       <c r="C119" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B120" s="14"/>
+      <c r="B120" s="35"/>
       <c r="C120" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B121" s="14"/>
+      <c r="B121" s="35"/>
       <c r="C121" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B122" s="14"/>
+      <c r="B122" s="35"/>
       <c r="C122" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B123" s="14"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B124" s="14"/>
+      <c r="B124" s="35"/>
       <c r="C124" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B125" s="14"/>
+      <c r="B125" s="35"/>
       <c r="C125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B126" s="14"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B127" s="14"/>
+      <c r="B127" s="35"/>
       <c r="C127" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B128" s="14"/>
+      <c r="B128" s="35"/>
       <c r="C128" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B129" s="14"/>
+      <c r="B129" s="35"/>
       <c r="C129" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B130" s="14"/>
+      <c r="B130" s="35"/>
       <c r="C130" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B131" s="15"/>
+      <c r="B131" s="36"/>
       <c r="C131" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="34" t="s">
         <v>49</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -4945,121 +6140,121 @@
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B133" s="14"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B134" s="14"/>
+      <c r="B134" s="35"/>
       <c r="C134" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B135" s="14"/>
+      <c r="B135" s="35"/>
       <c r="C135" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B136" s="14"/>
+      <c r="B136" s="35"/>
       <c r="C136" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B137" s="14"/>
+      <c r="B137" s="35"/>
       <c r="C137" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B138" s="14"/>
+      <c r="B138" s="35"/>
       <c r="C138" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B139" s="14"/>
+      <c r="B139" s="35"/>
       <c r="C139" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B140" s="14"/>
+      <c r="B140" s="35"/>
       <c r="C140" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B141" s="14"/>
+      <c r="B141" s="35"/>
       <c r="C141" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B142" s="14"/>
+      <c r="B142" s="35"/>
       <c r="C142" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B143" s="14"/>
+      <c r="B143" s="35"/>
       <c r="C143" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B144" s="14"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B145" s="14"/>
+      <c r="B145" s="35"/>
       <c r="C145" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B146" s="14"/>
+      <c r="B146" s="35"/>
       <c r="C146" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B147" s="14"/>
+      <c r="B147" s="35"/>
       <c r="C147" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B148" s="14"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B149" s="14"/>
+      <c r="B149" s="35"/>
       <c r="C149" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B150" s="14"/>
+      <c r="B150" s="35"/>
       <c r="C150" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B151" s="15"/>
+      <c r="B151" s="36"/>
       <c r="C151" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="34" t="s">
         <v>57</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -5067,121 +6262,121 @@
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B153" s="14"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B154" s="14"/>
+      <c r="B154" s="35"/>
       <c r="C154" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B155" s="14"/>
+      <c r="B155" s="35"/>
       <c r="C155" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B156" s="14"/>
+      <c r="B156" s="35"/>
       <c r="C156" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B157" s="14"/>
+      <c r="B157" s="35"/>
       <c r="C157" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B158" s="14"/>
+      <c r="B158" s="35"/>
       <c r="C158" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B159" s="14"/>
+      <c r="B159" s="35"/>
       <c r="C159" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B160" s="14"/>
+      <c r="B160" s="35"/>
       <c r="C160" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B161" s="14"/>
+      <c r="B161" s="35"/>
       <c r="C161" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B162" s="14"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B163" s="14"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B164" s="14"/>
+      <c r="B164" s="35"/>
       <c r="C164" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B165" s="14"/>
+      <c r="B165" s="35"/>
       <c r="C165" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B166" s="14"/>
+      <c r="B166" s="35"/>
       <c r="C166" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B167" s="14"/>
+      <c r="B167" s="35"/>
       <c r="C167" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B168" s="14"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B169" s="14"/>
+      <c r="B169" s="35"/>
       <c r="C169" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B170" s="14"/>
+      <c r="B170" s="35"/>
       <c r="C170" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B171" s="15"/>
+      <c r="B171" s="36"/>
       <c r="C171" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="34" t="s">
         <v>58</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -5189,139 +6384,139 @@
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B173" s="14"/>
+      <c r="B173" s="35"/>
       <c r="C173" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B174" s="14"/>
+      <c r="B174" s="35"/>
       <c r="C174" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B175" s="14"/>
+      <c r="B175" s="35"/>
       <c r="C175" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B176" s="14"/>
+      <c r="B176" s="35"/>
       <c r="C176" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177" s="14"/>
+      <c r="B177" s="35"/>
       <c r="C177" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B178" s="14"/>
+      <c r="B178" s="35"/>
       <c r="C178" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B179" s="14"/>
+      <c r="B179" s="35"/>
       <c r="C179" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B180" s="14"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B181" s="14"/>
+      <c r="B181" s="35"/>
       <c r="C181" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B182" s="14"/>
+      <c r="B182" s="35"/>
       <c r="C182" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B183" s="14"/>
+      <c r="B183" s="35"/>
       <c r="C183" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B184" s="14"/>
+      <c r="B184" s="35"/>
       <c r="C184" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B185" s="14"/>
+      <c r="B185" s="35"/>
       <c r="C185" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B186" s="14"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B187" s="14"/>
+      <c r="B187" s="35"/>
       <c r="C187" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188" s="14"/>
+      <c r="B188" s="35"/>
       <c r="C188" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B189" s="14"/>
+      <c r="B189" s="35"/>
       <c r="C189" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B190" s="14"/>
+      <c r="B190" s="35"/>
       <c r="C190" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B191" s="14"/>
+      <c r="B191" s="35"/>
       <c r="C191" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B192" s="14"/>
+      <c r="B192" s="35"/>
       <c r="C192" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B193" s="14"/>
+      <c r="B193" s="35"/>
       <c r="C193" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194" s="14"/>
+      <c r="B194" s="35"/>
       <c r="C194" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B195" s="15"/>
+      <c r="B195" s="36"/>
       <c r="C195" s="1" t="s">
         <v>78</v>
       </c>
@@ -5343,20 +6538,2317 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.4140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.4140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="33.75" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="14" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="24.4140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="68" max="70" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.9140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="32.25" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="28.9140625" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="8" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="7.9140625" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="100" max="102" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="14" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="14"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="14"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="14"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" s="14"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C20" s="14"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" s="14"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C22" s="14"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D49" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="14"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="9"/>
+      <c r="B55" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C55" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+      <c r="B59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="9"/>
+      <c r="B60" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+      <c r="B61" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+      <c r="B63" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="9"/>
+      <c r="B64" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="9"/>
+      <c r="B65" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="9"/>
+      <c r="B66" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="9"/>
+      <c r="B67" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="9"/>
+      <c r="B68" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+      <c r="B69" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="9"/>
+      <c r="B70" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="9"/>
+      <c r="B71" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="9"/>
+      <c r="B72" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="9"/>
+      <c r="B73" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="9"/>
+      <c r="B74" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="9"/>
+      <c r="B75" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="9"/>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="9"/>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="9"/>
+      <c r="B78" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="9"/>
+      <c r="B79" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="9"/>
+      <c r="B81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
+      <c r="B82" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="9"/>
+      <c r="B83" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:C82">
+    <sortState ref="B2:C100">
+      <sortCondition ref="B1:B100"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G142"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.08203125" customWidth="1"/>
+    <col min="2" max="2" width="39.83203125" customWidth="1"/>
+    <col min="3" max="4" width="41.5" customWidth="1"/>
+    <col min="6" max="6" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="F2" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+    </row>
+    <row r="42" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+    </row>
+    <row r="82" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" s="22"/>
+      <c r="D93" s="22"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="22"/>
+      <c r="D94" s="22"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" s="22"/>
+      <c r="D95" s="22"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C96" s="22"/>
+      <c r="D96" s="22"/>
+    </row>
+    <row r="97" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="25"/>
+      <c r="D97" s="25"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" s="22"/>
+      <c r="D99" s="22"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C100" s="22"/>
+      <c r="D100" s="22"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C105" s="22"/>
+      <c r="D105" s="22"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="22"/>
+      <c r="D106" s="22"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="22"/>
+      <c r="D107" s="22"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C108" s="22"/>
+      <c r="D108" s="22"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C109" s="22"/>
+      <c r="D109" s="22"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C113" s="22"/>
+      <c r="D113" s="22"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C118" s="22"/>
+      <c r="D118" s="22"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C119" s="22"/>
+      <c r="D119" s="22"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" s="22"/>
+      <c r="D120" s="22"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C122" s="22"/>
+      <c r="D122" s="22"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C123" s="22"/>
+      <c r="D123" s="22"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C125" s="22"/>
+      <c r="D125" s="22"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+    </row>
+    <row r="129" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C129" s="25"/>
+      <c r="D129" s="25"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="28"/>
+      <c r="D130" s="28"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="22"/>
+      <c r="D131" s="22"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" s="22"/>
+      <c r="D133" s="22"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C134" s="22"/>
+      <c r="D134" s="22"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="22"/>
+      <c r="D135" s="22"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="22"/>
+      <c r="D136" s="22"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C139" s="22"/>
+      <c r="D139" s="22"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C140" s="22"/>
+      <c r="D140" s="22"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="22"/>
+      <c r="D141" s="22"/>
+    </row>
+    <row r="142" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B142" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" s="25"/>
+      <c r="D142" s="25"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D142"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F245"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
     <col min="4" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5367,13 +8859,13 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="18">
+      <c r="B3" s="13">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>231</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -5381,10 +8873,10 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="18">
+      <c r="B4" s="13">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>232</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -5392,10 +8884,10 @@
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="18">
+      <c r="B5" s="13">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>238</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -5403,10 +8895,10 @@
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="18">
+      <c r="B6" s="13">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>233</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -5414,10 +8906,10 @@
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="18">
+      <c r="B7" s="13">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>236</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -5425,10 +8917,10 @@
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="18">
+      <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="15" t="s">
         <v>237</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -5436,10 +8928,10 @@
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="18">
+      <c r="B9" s="13">
         <v>7</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -5447,10 +8939,10 @@
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="18">
+      <c r="B10" s="13">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="14" t="s">
         <v>235</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -5458,10 +8950,10 @@
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="18">
+      <c r="B11" s="13">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>234</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -5469,10 +8961,10 @@
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="18">
+      <c r="B12" s="13">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="14" t="s">
         <v>240</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -5480,10 +8972,10 @@
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="18">
+      <c r="B13" s="13">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -5491,10 +8983,10 @@
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="18">
+      <c r="B14" s="13">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -5502,10 +8994,10 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="18">
+      <c r="B15" s="13">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -5513,10 +9005,10 @@
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="18">
+      <c r="B16" s="13">
         <v>14</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -5524,10 +9016,10 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="18">
+      <c r="B17" s="13">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -5535,10 +9027,10 @@
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="18">
+      <c r="B18" s="13">
         <v>16</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="14" t="s">
         <v>239</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -5546,18 +9038,18 @@
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="18">
+      <c r="B19" s="13">
         <v>17</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="18">
+      <c r="B20" s="13">
         <v>18</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6382,22 +9874,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E188"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
-    <col min="4" max="4" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="4.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6408,13 +9900,13 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>238</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -6425,7 +9917,7 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -6436,7 +9928,7 @@
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -6447,7 +9939,7 @@
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -6458,7 +9950,7 @@
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>257</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -6469,7 +9961,7 @@
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>256</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -6480,7 +9972,7 @@
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -6491,7 +9983,7 @@
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="14" t="s">
         <v>255</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -6502,7 +9994,7 @@
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -6513,7 +10005,7 @@
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -6524,7 +10016,7 @@
       <c r="B13" s="7">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -6535,7 +10027,7 @@
       <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -6546,7 +10038,7 @@
       <c r="B15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -6557,7 +10049,7 @@
       <c r="B16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -6568,7 +10060,7 @@
       <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>258</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -6579,7 +10071,7 @@
       <c r="B18" s="7">
         <v>16</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -6590,7 +10082,7 @@
       <c r="B19" s="7">
         <v>17</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -6601,7 +10093,7 @@
       <c r="B20" s="7">
         <v>18</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>235</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -6612,7 +10104,7 @@
       <c r="B21" s="7">
         <v>19</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="14" t="s">
         <v>234</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -6623,7 +10115,7 @@
       <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -6634,7 +10126,7 @@
       <c r="B23" s="7">
         <v>21</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -6645,7 +10137,7 @@
       <c r="B24" s="7">
         <v>22</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="14" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -6656,7 +10148,7 @@
       <c r="B25" s="7">
         <v>23</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -7194,22 +10686,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E141"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
-    <col min="4" max="4" width="2.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2.9140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
         <v>230</v>
       </c>
     </row>
@@ -7220,13 +10712,13 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -7237,7 +10729,7 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -7248,7 +10740,7 @@
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -7259,7 +10751,7 @@
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>242</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -7270,7 +10762,7 @@
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>241</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -7281,7 +10773,7 @@
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -7292,7 +10784,7 @@
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>243</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -7303,7 +10795,7 @@
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="14" t="s">
         <v>244</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -7314,7 +10806,7 @@
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>235</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -7325,7 +10817,7 @@
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="14" t="s">
         <v>234</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -7336,7 +10828,7 @@
       <c r="B13" s="7">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -7347,7 +10839,7 @@
       <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -7358,7 +10850,7 @@
       <c r="B15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -7369,7 +10861,7 @@
       <c r="B16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -7380,7 +10872,7 @@
       <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -7391,7 +10883,7 @@
       <c r="B18" s="7">
         <v>16</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -7402,7 +10894,7 @@
       <c r="B19" s="7">
         <v>17</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -7413,7 +10905,7 @@
       <c r="B20" s="7">
         <v>18</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -7424,7 +10916,7 @@
       <c r="B21" s="7">
         <v>19</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="14" t="s">
         <v>245</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -7435,7 +10927,7 @@
       <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="14" t="s">
         <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -7446,7 +10938,7 @@
       <c r="B23" s="7">
         <v>21</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="14" t="s">
         <v>249</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -7457,7 +10949,7 @@
       <c r="B24" s="7">
         <v>22</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="14" t="s">
         <v>250</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -7468,7 +10960,7 @@
       <c r="B25" s="7">
         <v>23</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="14" t="s">
         <v>246</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -7479,7 +10971,7 @@
       <c r="B26" s="7">
         <v>24</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="14" t="s">
         <v>247</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -7490,7 +10982,7 @@
       <c r="B27" s="7">
         <v>25</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="14" t="s">
         <v>248</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -7501,7 +10993,7 @@
       <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -7512,7 +11004,7 @@
       <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -7523,7 +11015,7 @@
       <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -7534,7 +11026,7 @@
       <c r="B31" s="7">
         <v>29</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -7545,7 +11037,7 @@
       <c r="B32" s="7">
         <v>30</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -7556,7 +11048,7 @@
       <c r="B33" s="7">
         <v>31</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="14" t="s">
         <v>251</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -7567,7 +11059,7 @@
       <c r="B34" s="7">
         <v>32</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="14" t="s">
         <v>252</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -7578,7 +11070,7 @@
       <c r="B35" s="7">
         <v>33</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="14" t="s">
         <v>253</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -7586,10 +11078,10 @@
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="18">
+      <c r="B36" s="13">
         <v>34</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="14" t="s">
         <v>254</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -7600,7 +11092,7 @@
       <c r="B37" s="7">
         <v>35</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="14" t="s">
         <v>51</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -7611,7 +11103,7 @@
       <c r="B38" s="7">
         <v>36</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -7622,7 +11114,7 @@
       <c r="B39" s="7">
         <v>37</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="14" t="s">
         <v>53</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -7633,7 +11125,7 @@
       <c r="B40" s="7">
         <v>38</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="14" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -7644,7 +11136,7 @@
       <c r="B41" s="7">
         <v>39</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="14" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7652,7 +11144,7 @@
       <c r="B42" s="7">
         <v>40</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7972,22 +11464,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:E62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
         <v>230</v>
       </c>
     </row>
@@ -7998,13 +11490,13 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>210</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -8015,7 +11507,7 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>276</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -8026,7 +11518,7 @@
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>211</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -8037,7 +11529,7 @@
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E6" s="10" t="s">
@@ -8048,7 +11540,7 @@
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>212</v>
       </c>
       <c r="E7" s="10" t="s">
@@ -8059,7 +11551,7 @@
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>213</v>
       </c>
     </row>
@@ -8067,7 +11559,7 @@
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>215</v>
       </c>
     </row>
@@ -8075,7 +11567,7 @@
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="14" t="s">
         <v>216</v>
       </c>
     </row>
@@ -8083,7 +11575,7 @@
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>217</v>
       </c>
       <c r="D11" t="s">
@@ -8094,7 +11586,7 @@
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="14" t="s">
         <v>218</v>
       </c>
     </row>
@@ -8102,7 +11594,7 @@
       <c r="B13" s="7">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>219</v>
       </c>
     </row>
@@ -8110,7 +11602,7 @@
       <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="14" t="s">
         <v>220</v>
       </c>
     </row>
@@ -8118,7 +11610,7 @@
       <c r="B15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>221</v>
       </c>
     </row>
@@ -8126,7 +11618,7 @@
       <c r="B16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="15" t="s">
         <v>222</v>
       </c>
     </row>
@@ -8134,7 +11626,7 @@
       <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>223</v>
       </c>
     </row>
@@ -8282,22 +11774,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F191"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
     <col min="4" max="4" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="37"/>
+      <c r="E1" s="38" t="s">
         <v>230</v>
       </c>
     </row>
@@ -8308,13 +11800,13 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>59</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -8325,7 +11817,7 @@
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -8336,7 +11828,7 @@
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -8347,7 +11839,7 @@
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -8358,7 +11850,7 @@
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>62</v>
       </c>
       <c r="E7" s="11">
@@ -8369,7 +11861,7 @@
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E8" s="11">
@@ -8380,7 +11872,7 @@
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>64</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -8391,7 +11883,7 @@
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="16" t="s">
         <v>68</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -8402,7 +11894,7 @@
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -8413,7 +11905,7 @@
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -8424,7 +11916,7 @@
       <c r="B13" s="7">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -8435,7 +11927,7 @@
       <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="14" t="s">
         <v>214</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -8446,7 +11938,7 @@
       <c r="B15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>72</v>
       </c>
     </row>
@@ -8454,7 +11946,7 @@
       <c r="B16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="9"/>
@@ -8463,7 +11955,7 @@
       <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="9"/>
@@ -8473,7 +11965,7 @@
       <c r="B18" s="7">
         <v>16</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="14" t="s">
         <v>73</v>
       </c>
     </row>
@@ -8481,7 +11973,7 @@
       <c r="B19" s="7">
         <v>17</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -8489,7 +11981,7 @@
       <c r="B20" s="7">
         <v>18</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -8497,7 +11989,7 @@
       <c r="B21" s="7">
         <v>19</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="14" t="s">
         <v>76</v>
       </c>
     </row>
@@ -8505,7 +11997,7 @@
       <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8513,7 +12005,7 @@
       <c r="B23" s="7">
         <v>21</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -8521,7 +12013,7 @@
       <c r="B24" s="7">
         <v>22</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="14" t="s">
         <v>264</v>
       </c>
     </row>
@@ -8529,7 +12021,7 @@
       <c r="B25" s="7">
         <v>23</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="14" t="s">
         <v>265</v>
       </c>
     </row>
@@ -8537,7 +12029,7 @@
       <c r="B26" s="7">
         <v>24</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="14" t="s">
         <v>266</v>
       </c>
     </row>
@@ -8545,7 +12037,7 @@
       <c r="B27" s="7">
         <v>25</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="14" t="s">
         <v>267</v>
       </c>
     </row>
@@ -8553,7 +12045,7 @@
       <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="14" t="s">
         <v>268</v>
       </c>
     </row>
@@ -8561,7 +12053,7 @@
       <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="14" t="s">
         <v>269</v>
       </c>
     </row>
@@ -8569,7 +12061,7 @@
       <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="14" t="s">
         <v>270</v>
       </c>
     </row>
@@ -8577,7 +12069,7 @@
       <c r="B31" s="7">
         <v>29</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="14" t="s">
         <v>271</v>
       </c>
     </row>
@@ -8585,7 +12077,7 @@
       <c r="B32" s="7">
         <v>30</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="16" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8593,7 +12085,7 @@
       <c r="B33" s="7">
         <v>31</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="14" t="s">
         <v>272</v>
       </c>
     </row>
@@ -8601,7 +12093,7 @@
       <c r="B34" s="7">
         <v>32</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="14" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9083,703 +12575,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E193"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="9.44140625" customWidth="1"/>
-    <col min="3" max="3" width="43.33203125" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="17"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="7">
-        <v>2</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="7">
-        <v>3</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="7">
-        <v>4</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="7">
-        <v>5</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="7">
-        <v>6</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="7">
-        <v>7</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7">
-        <v>8</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="7">
-        <v>9</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="7">
-        <v>10</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="7">
-        <v>11</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="7">
-        <v>12</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="7">
-        <v>13</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" s="5"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="5"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" s="5"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="5"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="5"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="5"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="5"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="5"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="5"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" s="5"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" s="5"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" s="5"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" s="5"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="5"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" s="5"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B42" s="5"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B43" s="5"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B44" s="5"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B45" s="5"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B46" s="5"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B47" s="5"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B48" s="5"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" s="5"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B50" s="5"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B51" s="5"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B52" s="5"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B53" s="5"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B54" s="5"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B55" s="5"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B56" s="5"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B57" s="5"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B58" s="5"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B59" s="5"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B60" s="5"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B61" s="5"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B62" s="5"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B63" s="5"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B64" s="5"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B65" s="5"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B66" s="5"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B67" s="5"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B68" s="5"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B69" s="5"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B70" s="5"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B71" s="5"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B72" s="5"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B73" s="5"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B74" s="5"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B75" s="5"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B76" s="5"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B77" s="5"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B78" s="5"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B79" s="5"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B80" s="5"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B81" s="5"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B82" s="5"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B83" s="5"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B84" s="5"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B85" s="5"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B86" s="5"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B87" s="5"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B88" s="5"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B89" s="5"/>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B90" s="5"/>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B91" s="5"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B92" s="5"/>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B93" s="5"/>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B94" s="6"/>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B95" s="6"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B96" s="6"/>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B97" s="6"/>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B98" s="6"/>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B99" s="6"/>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B100" s="6"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B101" s="6"/>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B102" s="6"/>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B103" s="6"/>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B104" s="6"/>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B105" s="6"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B106" s="6"/>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B107" s="6"/>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B108" s="6"/>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B109" s="6"/>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B110" s="6"/>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B111" s="6"/>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B112" s="6"/>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B113" s="6"/>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B114" s="6"/>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B115" s="6"/>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B116" s="6"/>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B117" s="6"/>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B118" s="6"/>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B119" s="6"/>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B120" s="6"/>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B121" s="6"/>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B122" s="6"/>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B123" s="6"/>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B124" s="6"/>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B125" s="6"/>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B126" s="6"/>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B127" s="6"/>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B128" s="6"/>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B129" s="6"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B130" s="6"/>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B131" s="6"/>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B132" s="6"/>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B133" s="6"/>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B134" s="6"/>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B135" s="6"/>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B136" s="6"/>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B137" s="6"/>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B138" s="6"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B139" s="6"/>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B140" s="6"/>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B141" s="6"/>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B142" s="6"/>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B143" s="6"/>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B144" s="6"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B145" s="6"/>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B146" s="6"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B147" s="6"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B148" s="6"/>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B149" s="6"/>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B150" s="6"/>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B151" s="6"/>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B152" s="6"/>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B153" s="6"/>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B154" s="6"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B155" s="6"/>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B156" s="6"/>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B157" s="6"/>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B158" s="6"/>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B159" s="6"/>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B160" s="6"/>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B161" s="6"/>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B162" s="6"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B163" s="6"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B164" s="6"/>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B165" s="6"/>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B166" s="6"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B167" s="6"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B168" s="6"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B169" s="6"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B170" s="6"/>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B171" s="6"/>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B172" s="6"/>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B173" s="6"/>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B174" s="6"/>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B175" s="6"/>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B176" s="6"/>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B177" s="6"/>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B178" s="6"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B179" s="6"/>
-    </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B180" s="6"/>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B181" s="6"/>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B182" s="6"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B183" s="6"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B184" s="6"/>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B185" s="6"/>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B186" s="6"/>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B187" s="6"/>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B188" s="6"/>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B189" s="6"/>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B190" s="6"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B191" s="6"/>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B192" s="6"/>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B193" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:E2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C3:C15">
-    <cfRule type="duplicateValues" dxfId="3" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C17">
-    <cfRule type="duplicateValues" dxfId="2" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C21">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/core/management/ปัญหางาน NG แยกประเภท.xlsx
+++ b/core/management/ปัญหางาน NG แยกประเภท.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24910" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="24910" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" state="hidden" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Loop" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cleancing data'!$B$1:$C$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DeectByCategory!$A$1:$D$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cleancing data'!$B$1:$C$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DeectByCategory!$A$1:$D$141</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="439">
   <si>
     <t>Scrap</t>
   </si>
@@ -312,9 +312,6 @@
     <t>ITSL-2</t>
   </si>
   <si>
-    <t>LINE  NO</t>
-  </si>
-  <si>
     <t>02</t>
   </si>
   <si>
@@ -441,9 +438,6 @@
     <t>CTA-S</t>
   </si>
   <si>
-    <t>EA4</t>
-  </si>
-  <si>
     <t>ETO6</t>
   </si>
   <si>
@@ -597,84 +591,6 @@
     <t>IOF</t>
   </si>
   <si>
-    <t>ITI4</t>
-  </si>
-  <si>
-    <t>ITO4</t>
-  </si>
-  <si>
-    <t>ITS-L1</t>
-  </si>
-  <si>
-    <t>ITS-L2</t>
-  </si>
-  <si>
-    <t>ITS-LB</t>
-  </si>
-  <si>
-    <t>IA8</t>
-  </si>
-  <si>
-    <t>IA8-SL</t>
-  </si>
-  <si>
-    <t>IFJL1,R1</t>
-  </si>
-  <si>
-    <t>IFJL2,R2</t>
-  </si>
-  <si>
-    <t>IFJR2</t>
-  </si>
-  <si>
-    <t>IFJL3,R3</t>
-  </si>
-  <si>
-    <t>IF1L,1R</t>
-  </si>
-  <si>
-    <t>IF1R</t>
-  </si>
-  <si>
-    <t>IF2L2R</t>
-  </si>
-  <si>
-    <t>TFL</t>
-  </si>
-  <si>
-    <t>CA8</t>
-  </si>
-  <si>
-    <t>CA8-S</t>
-  </si>
-  <si>
-    <t>CFL</t>
-  </si>
-  <si>
-    <t>CFR</t>
-  </si>
-  <si>
-    <t>A-TUS</t>
-  </si>
-  <si>
-    <t>CTI/O-S</t>
-  </si>
-  <si>
-    <t>CTU-S</t>
-  </si>
-  <si>
-    <t>ETI6</t>
-  </si>
-  <si>
-    <t>OFR</t>
-  </si>
-  <si>
-    <t>D-Tus</t>
-  </si>
-  <si>
-    <t>OTA-2</t>
-  </si>
-  <si>
     <t xml:space="preserve">เครื่อง Alarm </t>
   </si>
   <si>
@@ -1110,18 +1026,12 @@
     <t>Guideแตก</t>
   </si>
   <si>
-    <t>เศษSpecterติดเกลียวNut</t>
-  </si>
-  <si>
     <t>Used Spring</t>
   </si>
   <si>
     <t>สปริงใช้แล้ว</t>
   </si>
   <si>
-    <t>Spatter on Nut thread</t>
-  </si>
-  <si>
     <t>Vibration incomplete</t>
   </si>
   <si>
@@ -1167,9 +1077,6 @@
     <t>Slide smooth Low</t>
   </si>
   <si>
-    <t>Slide smooth</t>
-  </si>
-  <si>
     <t>Spot Patch is a gap.</t>
   </si>
   <si>
@@ -1189,6 +1096,270 @@
   </si>
   <si>
     <t>Swing torque NG</t>
+  </si>
+  <si>
+    <t>Defect code</t>
+  </si>
+  <si>
+    <t>DF001</t>
+  </si>
+  <si>
+    <t>DF002</t>
+  </si>
+  <si>
+    <t>DF003</t>
+  </si>
+  <si>
+    <t>DF004</t>
+  </si>
+  <si>
+    <t>DF005</t>
+  </si>
+  <si>
+    <t>DF006</t>
+  </si>
+  <si>
+    <t>DF007</t>
+  </si>
+  <si>
+    <t>DF008</t>
+  </si>
+  <si>
+    <t>DF009</t>
+  </si>
+  <si>
+    <t>DF010</t>
+  </si>
+  <si>
+    <t>DF011</t>
+  </si>
+  <si>
+    <t>DF012</t>
+  </si>
+  <si>
+    <t>DF013</t>
+  </si>
+  <si>
+    <t>DF014</t>
+  </si>
+  <si>
+    <t>DF015</t>
+  </si>
+  <si>
+    <t>DF016</t>
+  </si>
+  <si>
+    <t>DF017</t>
+  </si>
+  <si>
+    <t>DF018</t>
+  </si>
+  <si>
+    <t>DF019</t>
+  </si>
+  <si>
+    <t>DF020</t>
+  </si>
+  <si>
+    <t>DF021</t>
+  </si>
+  <si>
+    <t>DF022</t>
+  </si>
+  <si>
+    <t>DF023</t>
+  </si>
+  <si>
+    <t>DF024</t>
+  </si>
+  <si>
+    <t>DF025</t>
+  </si>
+  <si>
+    <t>DF026</t>
+  </si>
+  <si>
+    <t>DF027</t>
+  </si>
+  <si>
+    <t>DF028</t>
+  </si>
+  <si>
+    <t>DF029</t>
+  </si>
+  <si>
+    <t>DF030</t>
+  </si>
+  <si>
+    <t>DF031</t>
+  </si>
+  <si>
+    <t>DF032</t>
+  </si>
+  <si>
+    <t>DF033</t>
+  </si>
+  <si>
+    <t>DF034</t>
+  </si>
+  <si>
+    <t>DF035</t>
+  </si>
+  <si>
+    <t>DF036</t>
+  </si>
+  <si>
+    <t>DF037</t>
+  </si>
+  <si>
+    <t>DF038</t>
+  </si>
+  <si>
+    <t>DF039</t>
+  </si>
+  <si>
+    <t>DF040</t>
+  </si>
+  <si>
+    <t>DF041</t>
+  </si>
+  <si>
+    <t>DF042</t>
+  </si>
+  <si>
+    <t>DF043</t>
+  </si>
+  <si>
+    <t>DF044</t>
+  </si>
+  <si>
+    <t>DF045</t>
+  </si>
+  <si>
+    <t>DF046</t>
+  </si>
+  <si>
+    <t>DF047</t>
+  </si>
+  <si>
+    <t>DF048</t>
+  </si>
+  <si>
+    <t>DF049</t>
+  </si>
+  <si>
+    <t>DF050</t>
+  </si>
+  <si>
+    <t>DF051</t>
+  </si>
+  <si>
+    <t>DF052</t>
+  </si>
+  <si>
+    <t>DF053</t>
+  </si>
+  <si>
+    <t>DF054</t>
+  </si>
+  <si>
+    <t>DF055</t>
+  </si>
+  <si>
+    <t>DF056</t>
+  </si>
+  <si>
+    <t>DF057</t>
+  </si>
+  <si>
+    <t>DF058</t>
+  </si>
+  <si>
+    <t>DF059</t>
+  </si>
+  <si>
+    <t>DF060</t>
+  </si>
+  <si>
+    <t>DF061</t>
+  </si>
+  <si>
+    <t>DF062</t>
+  </si>
+  <si>
+    <t>DF063</t>
+  </si>
+  <si>
+    <t>DF064</t>
+  </si>
+  <si>
+    <t>DF065</t>
+  </si>
+  <si>
+    <t>DF066</t>
+  </si>
+  <si>
+    <t>DF067</t>
+  </si>
+  <si>
+    <t>DF068</t>
+  </si>
+  <si>
+    <t>DF069</t>
+  </si>
+  <si>
+    <t>DF070</t>
+  </si>
+  <si>
+    <t>DF071</t>
+  </si>
+  <si>
+    <t>DF072</t>
+  </si>
+  <si>
+    <t>DF073</t>
+  </si>
+  <si>
+    <t>DF074</t>
+  </si>
+  <si>
+    <t>DF075</t>
+  </si>
+  <si>
+    <t>DF076</t>
+  </si>
+  <si>
+    <t>DF077</t>
+  </si>
+  <si>
+    <t>DF078</t>
+  </si>
+  <si>
+    <t>DF079</t>
+  </si>
+  <si>
+    <t>DF080</t>
+  </si>
+  <si>
+    <t>DF081</t>
+  </si>
+  <si>
+    <t>DF082</t>
+  </si>
+  <si>
+    <t>DF083</t>
+  </si>
+  <si>
+    <t>Slide not smooth</t>
+  </si>
+  <si>
+    <t>Spatter on thread</t>
+  </si>
+  <si>
+    <t>เศษSpecterติดเกลียว</t>
+  </si>
+  <si>
+    <t>เศษ Specter ติดเกลียว</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1649,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1531,6 +1702,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1546,7 +1718,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2015,7 +2196,7 @@
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2032,7 +2213,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="35"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2047,7 +2228,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2062,7 +2243,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="35"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -2077,7 +2258,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
@@ -2092,7 +2273,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="35"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -2107,7 +2288,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2303,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2137,7 +2318,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="35"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -2152,7 +2333,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="35"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2348,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="35"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
@@ -2182,7 +2363,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="35"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2197,7 +2378,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="35"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
@@ -2212,7 +2393,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="35"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2227,7 +2408,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="35"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2242,7 +2423,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="35"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2257,7 +2438,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="35"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
@@ -2272,7 +2453,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="35"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2287,7 +2468,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="35"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
@@ -2302,7 +2483,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
@@ -2317,7 +2498,7 @@
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="35"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
@@ -2332,7 +2513,7 @@
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2347,7 +2528,7 @@
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="35" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2364,7 +2545,7 @@
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="35"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
@@ -2379,7 +2560,7 @@
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="35"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
@@ -2394,7 +2575,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="35"/>
+      <c r="B28" s="36"/>
       <c r="C28" s="1" t="s">
         <v>0</v>
       </c>
@@ -2409,7 +2590,7 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="35"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
@@ -2424,7 +2605,7 @@
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="35"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
@@ -2439,7 +2620,7 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="35"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
@@ -2454,7 +2635,7 @@
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="35"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
@@ -2469,7 +2650,7 @@
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
@@ -2484,7 +2665,7 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="35"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="1" t="s">
         <v>31</v>
       </c>
@@ -2499,7 +2680,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
@@ -2514,7 +2695,7 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="35"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="1" t="s">
         <v>14</v>
       </c>
@@ -2529,7 +2710,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="35"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,7 +2725,7 @@
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="35"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
@@ -2559,7 +2740,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="35"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2574,7 +2755,7 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="35"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
@@ -2589,7 +2770,7 @@
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="35"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
@@ -2604,7 +2785,7 @@
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="35"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
@@ -2619,7 +2800,7 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="35"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="1" t="s">
         <v>34</v>
       </c>
@@ -2634,7 +2815,7 @@
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="35"/>
+      <c r="B44" s="36"/>
       <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
@@ -2649,7 +2830,7 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="35"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="1" t="s">
         <v>25</v>
       </c>
@@ -2664,7 +2845,7 @@
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="36"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,7 +2860,7 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="35" t="s">
         <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -2696,7 +2877,7 @@
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="35"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="1" t="s">
         <v>38</v>
       </c>
@@ -2711,7 +2892,7 @@
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="35"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="1" t="s">
         <v>39</v>
       </c>
@@ -2726,7 +2907,7 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="35"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
@@ -2741,7 +2922,7 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="35"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
@@ -2756,7 +2937,7 @@
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="35"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="1" t="s">
         <v>28</v>
       </c>
@@ -2771,7 +2952,7 @@
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="35"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2967,7 @@
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="35"/>
+      <c r="B54" s="36"/>
       <c r="C54" s="1" t="s">
         <v>29</v>
       </c>
@@ -2801,7 +2982,7 @@
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="35"/>
+      <c r="B55" s="36"/>
       <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
@@ -2816,7 +2997,7 @@
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="35"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
@@ -2831,7 +3012,7 @@
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="35"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="1" t="s">
         <v>13</v>
       </c>
@@ -2846,7 +3027,7 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="35"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="1" t="s">
         <v>40</v>
       </c>
@@ -2861,7 +3042,7 @@
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="35"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="1" t="s">
         <v>31</v>
       </c>
@@ -2876,7 +3057,7 @@
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="35"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
@@ -2891,7 +3072,7 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="35"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="1" t="s">
         <v>14</v>
       </c>
@@ -2906,7 +3087,7 @@
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="35"/>
+      <c r="B62" s="36"/>
       <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
@@ -2921,7 +3102,7 @@
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="35"/>
+      <c r="B63" s="36"/>
       <c r="C63" s="1" t="s">
         <v>16</v>
       </c>
@@ -2936,7 +3117,7 @@
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="35"/>
+      <c r="B64" s="36"/>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
@@ -2951,7 +3132,7 @@
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="35"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="1" t="s">
         <v>18</v>
       </c>
@@ -2966,7 +3147,7 @@
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="35"/>
+      <c r="B66" s="36"/>
       <c r="C66" s="1" t="s">
         <v>12</v>
       </c>
@@ -2981,7 +3162,7 @@
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="35"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
@@ -2996,7 +3177,7 @@
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="35"/>
+      <c r="B68" s="36"/>
       <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
@@ -3011,7 +3192,7 @@
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="35"/>
+      <c r="B69" s="36"/>
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
@@ -3026,7 +3207,7 @@
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="35"/>
+      <c r="B70" s="36"/>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
@@ -3041,7 +3222,7 @@
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="35"/>
+      <c r="B71" s="36"/>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
@@ -3056,7 +3237,7 @@
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="35"/>
+      <c r="B72" s="36"/>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
@@ -3071,7 +3252,7 @@
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="35"/>
+      <c r="B73" s="36"/>
       <c r="C73" s="1" t="s">
         <v>34</v>
       </c>
@@ -3086,7 +3267,7 @@
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="35"/>
+      <c r="B74" s="36"/>
       <c r="C74" s="1" t="s">
         <v>35</v>
       </c>
@@ -3101,7 +3282,7 @@
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="35"/>
+      <c r="B75" s="36"/>
       <c r="C75" s="1" t="s">
         <v>41</v>
       </c>
@@ -3116,7 +3297,7 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="35"/>
+      <c r="B76" s="36"/>
       <c r="C76" s="1" t="s">
         <v>13</v>
       </c>
@@ -3131,7 +3312,7 @@
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="35"/>
+      <c r="B77" s="36"/>
       <c r="C77" s="1" t="s">
         <v>25</v>
       </c>
@@ -3146,7 +3327,7 @@
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="36"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="1" t="s">
         <v>26</v>
       </c>
@@ -3161,7 +3342,7 @@
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="34" t="s">
+      <c r="B79" s="35" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -3178,7 +3359,7 @@
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="35"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="1" t="s">
         <v>0</v>
       </c>
@@ -3193,7 +3374,7 @@
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="35"/>
+      <c r="B81" s="36"/>
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
@@ -3208,7 +3389,7 @@
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="35"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="1" t="s">
         <v>30</v>
       </c>
@@ -3223,7 +3404,7 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="35"/>
+      <c r="B83" s="36"/>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
@@ -3238,7 +3419,7 @@
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="35"/>
+      <c r="B84" s="36"/>
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
@@ -3253,7 +3434,7 @@
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="35"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="1" t="s">
         <v>13</v>
       </c>
@@ -3268,7 +3449,7 @@
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="35"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="1" t="s">
         <v>31</v>
       </c>
@@ -3283,7 +3464,7 @@
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="35"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="2" t="s">
         <v>52</v>
       </c>
@@ -3298,7 +3479,7 @@
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="35"/>
+      <c r="B88" s="36"/>
       <c r="C88" s="1" t="s">
         <v>14</v>
       </c>
@@ -3313,7 +3494,7 @@
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="35"/>
+      <c r="B89" s="36"/>
       <c r="C89" s="1" t="s">
         <v>15</v>
       </c>
@@ -3328,7 +3509,7 @@
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="35"/>
+      <c r="B90" s="36"/>
       <c r="C90" s="1" t="s">
         <v>18</v>
       </c>
@@ -3343,7 +3524,7 @@
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="35"/>
+      <c r="B91" s="36"/>
       <c r="C91" s="1" t="s">
         <v>12</v>
       </c>
@@ -3358,7 +3539,7 @@
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="35"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="1" t="s">
         <v>32</v>
       </c>
@@ -3373,7 +3554,7 @@
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="35"/>
+      <c r="B93" s="36"/>
       <c r="C93" s="1" t="s">
         <v>33</v>
       </c>
@@ -3385,7 +3566,7 @@
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="35"/>
+      <c r="B94" s="36"/>
       <c r="C94" s="1" t="s">
         <v>19</v>
       </c>
@@ -3397,7 +3578,7 @@
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="35"/>
+      <c r="B95" s="36"/>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
@@ -3409,7 +3590,7 @@
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B96" s="35"/>
+      <c r="B96" s="36"/>
       <c r="C96" s="1" t="s">
         <v>20</v>
       </c>
@@ -3421,7 +3602,7 @@
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B97" s="35"/>
+      <c r="B97" s="36"/>
       <c r="C97" s="1" t="s">
         <v>34</v>
       </c>
@@ -3433,7 +3614,7 @@
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="35"/>
+      <c r="B98" s="36"/>
       <c r="C98" s="1" t="s">
         <v>27</v>
       </c>
@@ -3445,7 +3626,7 @@
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="35"/>
+      <c r="B99" s="36"/>
       <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
@@ -3457,7 +3638,7 @@
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="35"/>
+      <c r="B100" s="36"/>
       <c r="C100" s="1" t="s">
         <v>44</v>
       </c>
@@ -3469,7 +3650,7 @@
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="35"/>
+      <c r="B101" s="36"/>
       <c r="C101" s="1" t="s">
         <v>45</v>
       </c>
@@ -3481,7 +3662,7 @@
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="35"/>
+      <c r="B102" s="36"/>
       <c r="C102" s="1" t="s">
         <v>47</v>
       </c>
@@ -3493,7 +3674,7 @@
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="35"/>
+      <c r="B103" s="36"/>
       <c r="C103" s="1" t="s">
         <v>46</v>
       </c>
@@ -3505,7 +3686,7 @@
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="35"/>
+      <c r="B104" s="36"/>
       <c r="C104" s="1" t="s">
         <v>25</v>
       </c>
@@ -3517,7 +3698,7 @@
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="36"/>
+      <c r="B105" s="37"/>
       <c r="C105" s="1" t="s">
         <v>26</v>
       </c>
@@ -3529,7 +3710,7 @@
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="34" t="s">
+      <c r="B106" s="35" t="s">
         <v>48</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -3543,7 +3724,7 @@
       </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="35"/>
+      <c r="B107" s="36"/>
       <c r="C107" s="1" t="s">
         <v>27</v>
       </c>
@@ -3555,7 +3736,7 @@
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="35"/>
+      <c r="B108" s="36"/>
       <c r="C108" s="1" t="s">
         <v>28</v>
       </c>
@@ -3567,7 +3748,7 @@
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="35"/>
+      <c r="B109" s="36"/>
       <c r="C109" s="1" t="s">
         <v>0</v>
       </c>
@@ -3579,7 +3760,7 @@
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="35"/>
+      <c r="B110" s="36"/>
       <c r="C110" s="1" t="s">
         <v>29</v>
       </c>
@@ -3591,7 +3772,7 @@
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="35"/>
+      <c r="B111" s="36"/>
       <c r="C111" s="1" t="s">
         <v>30</v>
       </c>
@@ -3603,7 +3784,7 @@
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="35"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
@@ -3615,7 +3796,7 @@
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
+      <c r="B113" s="36"/>
       <c r="C113" s="1" t="s">
         <v>12</v>
       </c>
@@ -3627,7 +3808,7 @@
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="35"/>
+      <c r="B114" s="36"/>
       <c r="C114" s="1" t="s">
         <v>13</v>
       </c>
@@ -3639,7 +3820,7 @@
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="35"/>
+      <c r="B115" s="36"/>
       <c r="C115" s="1" t="s">
         <v>31</v>
       </c>
@@ -3651,7 +3832,7 @@
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="35"/>
+      <c r="B116" s="36"/>
       <c r="C116" s="2" t="s">
         <v>52</v>
       </c>
@@ -3663,7 +3844,7 @@
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="35"/>
+      <c r="B117" s="36"/>
       <c r="C117" s="1" t="s">
         <v>14</v>
       </c>
@@ -3675,7 +3856,7 @@
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="35"/>
+      <c r="B118" s="36"/>
       <c r="C118" s="1" t="s">
         <v>15</v>
       </c>
@@ -3687,7 +3868,7 @@
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="35"/>
+      <c r="B119" s="36"/>
       <c r="C119" s="1" t="s">
         <v>16</v>
       </c>
@@ -3699,7 +3880,7 @@
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B120" s="35"/>
+      <c r="B120" s="36"/>
       <c r="C120" s="1" t="s">
         <v>18</v>
       </c>
@@ -3711,7 +3892,7 @@
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B121" s="35"/>
+      <c r="B121" s="36"/>
       <c r="C121" s="1" t="s">
         <v>12</v>
       </c>
@@ -3723,7 +3904,7 @@
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="35"/>
+      <c r="B122" s="36"/>
       <c r="C122" s="1" t="s">
         <v>32</v>
       </c>
@@ -3735,7 +3916,7 @@
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="35"/>
+      <c r="B123" s="36"/>
       <c r="C123" s="1" t="s">
         <v>33</v>
       </c>
@@ -3747,7 +3928,7 @@
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="35"/>
+      <c r="B124" s="36"/>
       <c r="C124" s="1" t="s">
         <v>19</v>
       </c>
@@ -3759,7 +3940,7 @@
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B125" s="35"/>
+      <c r="B125" s="36"/>
       <c r="C125" s="1" t="s">
         <v>10</v>
       </c>
@@ -3771,7 +3952,7 @@
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="35"/>
+      <c r="B126" s="36"/>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
@@ -3783,7 +3964,7 @@
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="35"/>
+      <c r="B127" s="36"/>
       <c r="C127" s="1" t="s">
         <v>20</v>
       </c>
@@ -3795,7 +3976,7 @@
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B128" s="35"/>
+      <c r="B128" s="36"/>
       <c r="C128" s="1" t="s">
         <v>34</v>
       </c>
@@ -3807,7 +3988,7 @@
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B129" s="35"/>
+      <c r="B129" s="36"/>
       <c r="C129" s="1" t="s">
         <v>35</v>
       </c>
@@ -3819,7 +4000,7 @@
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B130" s="35"/>
+      <c r="B130" s="36"/>
       <c r="C130" s="1" t="s">
         <v>25</v>
       </c>
@@ -3831,7 +4012,7 @@
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B131" s="36"/>
+      <c r="B131" s="37"/>
       <c r="C131" s="1" t="s">
         <v>26</v>
       </c>
@@ -3843,7 +4024,7 @@
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="34" t="s">
+      <c r="B132" s="35" t="s">
         <v>49</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -3857,7 +4038,7 @@
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="35"/>
+      <c r="B133" s="36"/>
       <c r="C133" s="1" t="s">
         <v>50</v>
       </c>
@@ -3869,7 +4050,7 @@
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="35"/>
+      <c r="B134" s="36"/>
       <c r="C134" s="1" t="s">
         <v>51</v>
       </c>
@@ -3881,7 +4062,7 @@
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="35"/>
+      <c r="B135" s="36"/>
       <c r="C135" s="1" t="s">
         <v>52</v>
       </c>
@@ -3893,7 +4074,7 @@
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="35"/>
+      <c r="B136" s="36"/>
       <c r="C136" s="1" t="s">
         <v>31</v>
       </c>
@@ -3905,7 +4086,7 @@
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="35"/>
+      <c r="B137" s="36"/>
       <c r="C137" s="1" t="s">
         <v>53</v>
       </c>
@@ -3917,7 +4098,7 @@
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="35"/>
+      <c r="B138" s="36"/>
       <c r="C138" s="1" t="s">
         <v>54</v>
       </c>
@@ -3929,7 +4110,7 @@
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B139" s="35"/>
+      <c r="B139" s="36"/>
       <c r="C139" s="1" t="s">
         <v>55</v>
       </c>
@@ -3941,7 +4122,7 @@
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B140" s="35"/>
+      <c r="B140" s="36"/>
       <c r="C140" s="1" t="s">
         <v>24</v>
       </c>
@@ -3953,7 +4134,7 @@
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="35"/>
+      <c r="B141" s="36"/>
       <c r="C141" s="1" t="s">
         <v>15</v>
       </c>
@@ -3965,7 +4146,7 @@
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="35"/>
+      <c r="B142" s="36"/>
       <c r="C142" s="1" t="s">
         <v>16</v>
       </c>
@@ -3977,7 +4158,7 @@
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B143" s="35"/>
+      <c r="B143" s="36"/>
       <c r="C143" s="1" t="s">
         <v>17</v>
       </c>
@@ -3989,7 +4170,7 @@
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B144" s="35"/>
+      <c r="B144" s="36"/>
       <c r="C144" s="1" t="s">
         <v>18</v>
       </c>
@@ -4001,7 +4182,7 @@
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B145" s="35"/>
+      <c r="B145" s="36"/>
       <c r="C145" s="1" t="s">
         <v>12</v>
       </c>
@@ -4013,7 +4194,7 @@
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B146" s="35"/>
+      <c r="B146" s="36"/>
       <c r="C146" s="1" t="s">
         <v>20</v>
       </c>
@@ -4025,7 +4206,7 @@
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B147" s="35"/>
+      <c r="B147" s="36"/>
       <c r="C147" s="1" t="s">
         <v>32</v>
       </c>
@@ -4037,7 +4218,7 @@
       </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B148" s="35"/>
+      <c r="B148" s="36"/>
       <c r="C148" s="1" t="s">
         <v>10</v>
       </c>
@@ -4049,7 +4230,7 @@
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B149" s="35"/>
+      <c r="B149" s="36"/>
       <c r="C149" s="1" t="s">
         <v>56</v>
       </c>
@@ -4061,7 +4242,7 @@
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B150" s="35"/>
+      <c r="B150" s="36"/>
       <c r="C150" s="1" t="s">
         <v>25</v>
       </c>
@@ -4073,7 +4254,7 @@
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B151" s="36"/>
+      <c r="B151" s="37"/>
       <c r="C151" s="1" t="s">
         <v>26</v>
       </c>
@@ -4085,7 +4266,7 @@
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B152" s="34" t="s">
+      <c r="B152" s="35" t="s">
         <v>57</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -4099,7 +4280,7 @@
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B153" s="35"/>
+      <c r="B153" s="36"/>
       <c r="C153" s="1" t="s">
         <v>50</v>
       </c>
@@ -4111,7 +4292,7 @@
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B154" s="35"/>
+      <c r="B154" s="36"/>
       <c r="C154" s="1" t="s">
         <v>51</v>
       </c>
@@ -4123,7 +4304,7 @@
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B155" s="35"/>
+      <c r="B155" s="36"/>
       <c r="C155" s="1" t="s">
         <v>52</v>
       </c>
@@ -4135,7 +4316,7 @@
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B156" s="35"/>
+      <c r="B156" s="36"/>
       <c r="C156" s="1" t="s">
         <v>31</v>
       </c>
@@ -4147,7 +4328,7 @@
       </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B157" s="35"/>
+      <c r="B157" s="36"/>
       <c r="C157" s="1" t="s">
         <v>53</v>
       </c>
@@ -4159,7 +4340,7 @@
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B158" s="35"/>
+      <c r="B158" s="36"/>
       <c r="C158" s="1" t="s">
         <v>54</v>
       </c>
@@ -4171,7 +4352,7 @@
       </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B159" s="35"/>
+      <c r="B159" s="36"/>
       <c r="C159" s="1" t="s">
         <v>55</v>
       </c>
@@ -4183,7 +4364,7 @@
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B160" s="35"/>
+      <c r="B160" s="36"/>
       <c r="C160" s="1" t="s">
         <v>24</v>
       </c>
@@ -4195,7 +4376,7 @@
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B161" s="35"/>
+      <c r="B161" s="36"/>
       <c r="C161" s="1" t="s">
         <v>15</v>
       </c>
@@ -4207,7 +4388,7 @@
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B162" s="35"/>
+      <c r="B162" s="36"/>
       <c r="C162" s="1" t="s">
         <v>16</v>
       </c>
@@ -4219,7 +4400,7 @@
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B163" s="35"/>
+      <c r="B163" s="36"/>
       <c r="C163" s="1" t="s">
         <v>17</v>
       </c>
@@ -4231,7 +4412,7 @@
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B164" s="35"/>
+      <c r="B164" s="36"/>
       <c r="C164" s="1" t="s">
         <v>18</v>
       </c>
@@ -4243,7 +4424,7 @@
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B165" s="35"/>
+      <c r="B165" s="36"/>
       <c r="C165" s="1" t="s">
         <v>12</v>
       </c>
@@ -4255,7 +4436,7 @@
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B166" s="35"/>
+      <c r="B166" s="36"/>
       <c r="C166" s="1" t="s">
         <v>20</v>
       </c>
@@ -4267,7 +4448,7 @@
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B167" s="35"/>
+      <c r="B167" s="36"/>
       <c r="C167" s="1" t="s">
         <v>32</v>
       </c>
@@ -4279,7 +4460,7 @@
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B168" s="35"/>
+      <c r="B168" s="36"/>
       <c r="C168" s="1" t="s">
         <v>10</v>
       </c>
@@ -4291,7 +4472,7 @@
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B169" s="35"/>
+      <c r="B169" s="36"/>
       <c r="C169" s="1" t="s">
         <v>56</v>
       </c>
@@ -4303,7 +4484,7 @@
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B170" s="35"/>
+      <c r="B170" s="36"/>
       <c r="C170" s="1" t="s">
         <v>25</v>
       </c>
@@ -4315,7 +4496,7 @@
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B171" s="36"/>
+      <c r="B171" s="37"/>
       <c r="C171" s="1" t="s">
         <v>26</v>
       </c>
@@ -4327,7 +4508,7 @@
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B172" s="34" t="s">
+      <c r="B172" s="35" t="s">
         <v>58</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -4341,7 +4522,7 @@
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B173" s="35"/>
+      <c r="B173" s="36"/>
       <c r="C173" s="1" t="s">
         <v>60</v>
       </c>
@@ -4353,7 +4534,7 @@
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B174" s="35"/>
+      <c r="B174" s="36"/>
       <c r="C174" s="1" t="s">
         <v>61</v>
       </c>
@@ -4365,7 +4546,7 @@
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B175" s="35"/>
+      <c r="B175" s="36"/>
       <c r="C175" s="1" t="s">
         <v>32</v>
       </c>
@@ -4377,7 +4558,7 @@
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B176" s="35"/>
+      <c r="B176" s="36"/>
       <c r="C176" s="1" t="s">
         <v>62</v>
       </c>
@@ -4389,7 +4570,7 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B177" s="35"/>
+      <c r="B177" s="36"/>
       <c r="C177" s="1" t="s">
         <v>63</v>
       </c>
@@ -4401,7 +4582,7 @@
       </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B178" s="35"/>
+      <c r="B178" s="36"/>
       <c r="C178" s="1" t="s">
         <v>64</v>
       </c>
@@ -4413,7 +4594,7 @@
       </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B179" s="35"/>
+      <c r="B179" s="36"/>
       <c r="C179" s="1" t="s">
         <v>65</v>
       </c>
@@ -4425,7 +4606,7 @@
       </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B180" s="35"/>
+      <c r="B180" s="36"/>
       <c r="C180" s="1" t="s">
         <v>66</v>
       </c>
@@ -4437,7 +4618,7 @@
       </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B181" s="35"/>
+      <c r="B181" s="36"/>
       <c r="C181" s="1" t="s">
         <v>67</v>
       </c>
@@ -4449,7 +4630,7 @@
       </c>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B182" s="35"/>
+      <c r="B182" s="36"/>
       <c r="C182" s="1" t="s">
         <v>68</v>
       </c>
@@ -4461,7 +4642,7 @@
       </c>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B183" s="35"/>
+      <c r="B183" s="36"/>
       <c r="C183" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,7 +4654,7 @@
       </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B184" s="35"/>
+      <c r="B184" s="36"/>
       <c r="C184" s="1" t="s">
         <v>10</v>
       </c>
@@ -4485,7 +4666,7 @@
       </c>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B185" s="35"/>
+      <c r="B185" s="36"/>
       <c r="C185" s="1" t="s">
         <v>70</v>
       </c>
@@ -4497,7 +4678,7 @@
       </c>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B186" s="35"/>
+      <c r="B186" s="36"/>
       <c r="C186" s="1" t="s">
         <v>71</v>
       </c>
@@ -4509,7 +4690,7 @@
       </c>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B187" s="35"/>
+      <c r="B187" s="36"/>
       <c r="C187" s="1" t="s">
         <v>72</v>
       </c>
@@ -4521,7 +4702,7 @@
       </c>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B188" s="35"/>
+      <c r="B188" s="36"/>
       <c r="C188" s="1" t="s">
         <v>34</v>
       </c>
@@ -4533,7 +4714,7 @@
       </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B189" s="35"/>
+      <c r="B189" s="36"/>
       <c r="C189" s="1" t="s">
         <v>12</v>
       </c>
@@ -4545,7 +4726,7 @@
       </c>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B190" s="35"/>
+      <c r="B190" s="36"/>
       <c r="C190" s="1" t="s">
         <v>73</v>
       </c>
@@ -4557,7 +4738,7 @@
       </c>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B191" s="35"/>
+      <c r="B191" s="36"/>
       <c r="C191" s="1" t="s">
         <v>74</v>
       </c>
@@ -4569,7 +4750,7 @@
       </c>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B192" s="35"/>
+      <c r="B192" s="36"/>
       <c r="C192" s="1" t="s">
         <v>75</v>
       </c>
@@ -4581,7 +4762,7 @@
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B193" s="35"/>
+      <c r="B193" s="36"/>
       <c r="C193" s="1" t="s">
         <v>76</v>
       </c>
@@ -4593,7 +4774,7 @@
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B194" s="35"/>
+      <c r="B194" s="36"/>
       <c r="C194" s="1" t="s">
         <v>77</v>
       </c>
@@ -4605,7 +4786,7 @@
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B195" s="36"/>
+      <c r="B195" s="37"/>
       <c r="C195" s="1" t="s">
         <v>78</v>
       </c>
@@ -4642,12 +4823,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4657,7 +4838,7 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
@@ -4667,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -4678,7 +4859,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -4689,7 +4870,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -4700,7 +4881,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -4708,7 +4889,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -4732,7 +4913,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -4740,7 +4921,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -4748,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -4756,7 +4937,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -5348,7 +5529,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5356,133 +5537,133 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="35"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="35"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="35"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="35"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="35"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="35"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="35"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="35"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="35"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="35"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="35"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="35"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="35"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="35"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="35"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="35"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="35"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="35" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -5490,133 +5671,133 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="35"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="35"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="35"/>
+      <c r="B28" s="36"/>
       <c r="C28" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="35"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="35"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="35"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="35"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="35"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="35"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" s="35"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="35"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B39" s="35"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" s="35"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B41" s="35"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B42" s="35"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B43" s="35"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" s="35"/>
+      <c r="B44" s="36"/>
       <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B45" s="35"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B46" s="36"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="35" t="s">
         <v>36</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -5624,193 +5805,193 @@
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B48" s="35"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="35"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" s="35"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B51" s="35"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B52" s="35"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B53" s="35"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B54" s="35"/>
+      <c r="B54" s="36"/>
       <c r="C54" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B55" s="35"/>
+      <c r="B55" s="36"/>
       <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="35"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B57" s="35"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B58" s="35"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="35"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B60" s="35"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B61" s="35"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B62" s="35"/>
+      <c r="B62" s="36"/>
       <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="35"/>
+      <c r="B63" s="36"/>
       <c r="C63" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B64" s="35"/>
+      <c r="B64" s="36"/>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B65" s="35"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B66" s="35"/>
+      <c r="B66" s="36"/>
       <c r="C66" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B67" s="35"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B68" s="35"/>
+      <c r="B68" s="36"/>
       <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B69" s="35"/>
+      <c r="B69" s="36"/>
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B70" s="35"/>
+      <c r="B70" s="36"/>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B71" s="35"/>
+      <c r="B71" s="36"/>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B72" s="35"/>
+      <c r="B72" s="36"/>
       <c r="C72" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B73" s="35"/>
+      <c r="B73" s="36"/>
       <c r="C73" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B74" s="35"/>
+      <c r="B74" s="36"/>
       <c r="C74" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B75" s="35"/>
+      <c r="B75" s="36"/>
       <c r="C75" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B76" s="35"/>
+      <c r="B76" s="36"/>
       <c r="C76" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B77" s="35"/>
+      <c r="B77" s="36"/>
       <c r="C77" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B78" s="36"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B79" s="34" t="s">
+      <c r="B79" s="35" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -5818,163 +5999,163 @@
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B80" s="35"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B81" s="35"/>
+      <c r="B81" s="36"/>
       <c r="C81" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B82" s="35"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B83" s="35"/>
+      <c r="B83" s="36"/>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84" s="35"/>
+      <c r="B84" s="36"/>
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B85" s="35"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B86" s="35"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B87" s="35"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B88" s="35"/>
+      <c r="B88" s="36"/>
       <c r="C88" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B89" s="35"/>
+      <c r="B89" s="36"/>
       <c r="C89" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B90" s="35"/>
+      <c r="B90" s="36"/>
       <c r="C90" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B91" s="35"/>
+      <c r="B91" s="36"/>
       <c r="C91" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B92" s="35"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B93" s="35"/>
+      <c r="B93" s="36"/>
       <c r="C93" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B94" s="35"/>
+      <c r="B94" s="36"/>
       <c r="C94" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" s="35"/>
+      <c r="B95" s="36"/>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B96" s="35"/>
+      <c r="B96" s="36"/>
       <c r="C96" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" s="35"/>
+      <c r="B97" s="36"/>
       <c r="C97" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98" s="35"/>
+      <c r="B98" s="36"/>
       <c r="C98" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99" s="35"/>
+      <c r="B99" s="36"/>
       <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="35"/>
+      <c r="B100" s="36"/>
       <c r="C100" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B101" s="35"/>
+      <c r="B101" s="36"/>
       <c r="C101" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B102" s="35"/>
+      <c r="B102" s="36"/>
       <c r="C102" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B103" s="35"/>
+      <c r="B103" s="36"/>
       <c r="C103" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B104" s="35"/>
+      <c r="B104" s="36"/>
       <c r="C104" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B105" s="36"/>
+      <c r="B105" s="37"/>
       <c r="C105" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B106" s="34" t="s">
+      <c r="B106" s="35" t="s">
         <v>48</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -5982,157 +6163,157 @@
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B107" s="35"/>
+      <c r="B107" s="36"/>
       <c r="C107" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B108" s="35"/>
+      <c r="B108" s="36"/>
       <c r="C108" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B109" s="35"/>
+      <c r="B109" s="36"/>
       <c r="C109" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B110" s="35"/>
+      <c r="B110" s="36"/>
       <c r="C110" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B111" s="35"/>
+      <c r="B111" s="36"/>
       <c r="C111" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B112" s="35"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
+      <c r="B113" s="36"/>
       <c r="C113" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B114" s="35"/>
+      <c r="B114" s="36"/>
       <c r="C114" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B115" s="35"/>
+      <c r="B115" s="36"/>
       <c r="C115" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B116" s="35"/>
+      <c r="B116" s="36"/>
       <c r="C116" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B117" s="35"/>
+      <c r="B117" s="36"/>
       <c r="C117" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B118" s="35"/>
+      <c r="B118" s="36"/>
       <c r="C118" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B119" s="35"/>
+      <c r="B119" s="36"/>
       <c r="C119" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B120" s="35"/>
+      <c r="B120" s="36"/>
       <c r="C120" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B121" s="35"/>
+      <c r="B121" s="36"/>
       <c r="C121" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B122" s="35"/>
+      <c r="B122" s="36"/>
       <c r="C122" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B123" s="35"/>
+      <c r="B123" s="36"/>
       <c r="C123" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B124" s="35"/>
+      <c r="B124" s="36"/>
       <c r="C124" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B125" s="35"/>
+      <c r="B125" s="36"/>
       <c r="C125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B126" s="35"/>
+      <c r="B126" s="36"/>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B127" s="35"/>
+      <c r="B127" s="36"/>
       <c r="C127" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B128" s="35"/>
+      <c r="B128" s="36"/>
       <c r="C128" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B129" s="35"/>
+      <c r="B129" s="36"/>
       <c r="C129" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B130" s="35"/>
+      <c r="B130" s="36"/>
       <c r="C130" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B131" s="36"/>
+      <c r="B131" s="37"/>
       <c r="C131" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B132" s="34" t="s">
+      <c r="B132" s="35" t="s">
         <v>49</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -6140,121 +6321,121 @@
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B133" s="35"/>
+      <c r="B133" s="36"/>
       <c r="C133" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B134" s="35"/>
+      <c r="B134" s="36"/>
       <c r="C134" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B135" s="35"/>
+      <c r="B135" s="36"/>
       <c r="C135" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B136" s="35"/>
+      <c r="B136" s="36"/>
       <c r="C136" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B137" s="35"/>
+      <c r="B137" s="36"/>
       <c r="C137" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B138" s="35"/>
+      <c r="B138" s="36"/>
       <c r="C138" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B139" s="35"/>
+      <c r="B139" s="36"/>
       <c r="C139" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B140" s="35"/>
+      <c r="B140" s="36"/>
       <c r="C140" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B141" s="35"/>
+      <c r="B141" s="36"/>
       <c r="C141" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B142" s="35"/>
+      <c r="B142" s="36"/>
       <c r="C142" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B143" s="35"/>
+      <c r="B143" s="36"/>
       <c r="C143" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B144" s="35"/>
+      <c r="B144" s="36"/>
       <c r="C144" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B145" s="35"/>
+      <c r="B145" s="36"/>
       <c r="C145" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B146" s="35"/>
+      <c r="B146" s="36"/>
       <c r="C146" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B147" s="35"/>
+      <c r="B147" s="36"/>
       <c r="C147" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B148" s="35"/>
+      <c r="B148" s="36"/>
       <c r="C148" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B149" s="35"/>
+      <c r="B149" s="36"/>
       <c r="C149" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B150" s="35"/>
+      <c r="B150" s="36"/>
       <c r="C150" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B151" s="36"/>
+      <c r="B151" s="37"/>
       <c r="C151" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B152" s="34" t="s">
+      <c r="B152" s="35" t="s">
         <v>57</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -6262,121 +6443,121 @@
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B153" s="35"/>
+      <c r="B153" s="36"/>
       <c r="C153" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B154" s="35"/>
+      <c r="B154" s="36"/>
       <c r="C154" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B155" s="35"/>
+      <c r="B155" s="36"/>
       <c r="C155" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B156" s="35"/>
+      <c r="B156" s="36"/>
       <c r="C156" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B157" s="35"/>
+      <c r="B157" s="36"/>
       <c r="C157" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B158" s="35"/>
+      <c r="B158" s="36"/>
       <c r="C158" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B159" s="35"/>
+      <c r="B159" s="36"/>
       <c r="C159" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B160" s="35"/>
+      <c r="B160" s="36"/>
       <c r="C160" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B161" s="35"/>
+      <c r="B161" s="36"/>
       <c r="C161" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B162" s="35"/>
+      <c r="B162" s="36"/>
       <c r="C162" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B163" s="35"/>
+      <c r="B163" s="36"/>
       <c r="C163" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B164" s="35"/>
+      <c r="B164" s="36"/>
       <c r="C164" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B165" s="35"/>
+      <c r="B165" s="36"/>
       <c r="C165" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B166" s="35"/>
+      <c r="B166" s="36"/>
       <c r="C166" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B167" s="35"/>
+      <c r="B167" s="36"/>
       <c r="C167" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B168" s="35"/>
+      <c r="B168" s="36"/>
       <c r="C168" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B169" s="35"/>
+      <c r="B169" s="36"/>
       <c r="C169" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B170" s="35"/>
+      <c r="B170" s="36"/>
       <c r="C170" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B171" s="36"/>
+      <c r="B171" s="37"/>
       <c r="C171" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B172" s="34" t="s">
+      <c r="B172" s="35" t="s">
         <v>58</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -6384,139 +6565,139 @@
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B173" s="35"/>
+      <c r="B173" s="36"/>
       <c r="C173" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B174" s="35"/>
+      <c r="B174" s="36"/>
       <c r="C174" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B175" s="35"/>
+      <c r="B175" s="36"/>
       <c r="C175" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B176" s="35"/>
+      <c r="B176" s="36"/>
       <c r="C176" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177" s="35"/>
+      <c r="B177" s="36"/>
       <c r="C177" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B178" s="35"/>
+      <c r="B178" s="36"/>
       <c r="C178" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B179" s="35"/>
+      <c r="B179" s="36"/>
       <c r="C179" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B180" s="35"/>
+      <c r="B180" s="36"/>
       <c r="C180" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B181" s="35"/>
+      <c r="B181" s="36"/>
       <c r="C181" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B182" s="35"/>
+      <c r="B182" s="36"/>
       <c r="C182" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B183" s="35"/>
+      <c r="B183" s="36"/>
       <c r="C183" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B184" s="35"/>
+      <c r="B184" s="36"/>
       <c r="C184" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B185" s="35"/>
+      <c r="B185" s="36"/>
       <c r="C185" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B186" s="35"/>
+      <c r="B186" s="36"/>
       <c r="C186" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B187" s="35"/>
+      <c r="B187" s="36"/>
       <c r="C187" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188" s="35"/>
+      <c r="B188" s="36"/>
       <c r="C188" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B189" s="35"/>
+      <c r="B189" s="36"/>
       <c r="C189" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B190" s="35"/>
+      <c r="B190" s="36"/>
       <c r="C190" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B191" s="35"/>
+      <c r="B191" s="36"/>
       <c r="C191" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B192" s="35"/>
+      <c r="B192" s="36"/>
       <c r="C192" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B193" s="35"/>
+      <c r="B193" s="36"/>
       <c r="C193" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194" s="35"/>
+      <c r="B194" s="36"/>
       <c r="C194" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B195" s="36"/>
+      <c r="B195" s="37"/>
       <c r="C195" s="1" t="s">
         <v>78</v>
       </c>
@@ -6541,8 +6722,8 @@
   <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="5" customWidth="1"/>
+    <col min="2" max="2" width="35.4140625" customWidth="1"/>
     <col min="3" max="3" width="34.83203125" customWidth="1"/>
     <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
@@ -6648,42 +6829,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
+        <v>351</v>
+      </c>
       <c r="B1" s="31" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
+      <c r="A2" s="7" t="s">
+        <v>352</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
+      <c r="A3" s="7" t="s">
+        <v>353</v>
+      </c>
       <c r="B3" s="1" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="7" t="s">
+        <v>354</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="7" t="s">
+        <v>355</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
@@ -6692,690 +6884,846 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="B6" s="1" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="7" t="s">
+        <v>357</v>
+      </c>
       <c r="B7" s="1" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="7" t="s">
+        <v>358</v>
+      </c>
       <c r="B8" s="1" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
+      <c r="A9" s="7" t="s">
+        <v>359</v>
+      </c>
       <c r="B9" s="1" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="7" t="s">
+        <v>360</v>
+      </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="B11" s="1" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
+      <c r="A12" s="7" t="s">
+        <v>362</v>
+      </c>
       <c r="B12" s="17" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
+      <c r="A13" s="7" t="s">
+        <v>363</v>
+      </c>
       <c r="B13" s="31" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
+      <c r="A14" s="7" t="s">
+        <v>364</v>
+      </c>
       <c r="B14" s="1" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
+      <c r="A15" s="7" t="s">
+        <v>365</v>
+      </c>
       <c r="B15" s="1" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="B16" s="1" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
+      <c r="A17" s="7" t="s">
+        <v>367</v>
+      </c>
       <c r="B17" s="1" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
+      <c r="A18" s="7" t="s">
+        <v>368</v>
+      </c>
       <c r="B18" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="14"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+      <c r="A19" s="7" t="s">
+        <v>369</v>
+      </c>
       <c r="B19" s="1" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="C19" s="14"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
+      <c r="A20" s="7" t="s">
+        <v>370</v>
+      </c>
       <c r="B20" s="1" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="C20" s="14"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
+      <c r="A21" s="7" t="s">
+        <v>371</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
+      <c r="A22" s="7" t="s">
+        <v>372</v>
+      </c>
       <c r="B22" s="1" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="C22" s="14"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
+      <c r="A23" s="7" t="s">
+        <v>373</v>
+      </c>
       <c r="B23" s="1" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="C23" s="14"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
+      <c r="A24" s="7" t="s">
+        <v>374</v>
+      </c>
       <c r="B24" s="1" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
+      <c r="A25" s="7" t="s">
+        <v>375</v>
+      </c>
       <c r="B25" s="10" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
+      <c r="A26" s="7" t="s">
+        <v>376</v>
+      </c>
       <c r="B26" s="10" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
+      <c r="A27" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="B27" s="1" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
+      <c r="A28" s="7" t="s">
+        <v>378</v>
+      </c>
       <c r="B28" s="1" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
+      <c r="A29" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="B29" s="1" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C30" s="1" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="1" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C37" s="1" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
+      <c r="A38" s="7" t="s">
+        <v>388</v>
+      </c>
       <c r="B38" s="1" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
+      <c r="A39" s="7" t="s">
+        <v>389</v>
+      </c>
       <c r="B39" s="32" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
+      <c r="A40" s="7" t="s">
+        <v>390</v>
+      </c>
       <c r="B40" s="32" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
+      <c r="A41" s="7" t="s">
+        <v>391</v>
+      </c>
       <c r="B41" s="32" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
+      <c r="A42" s="7" t="s">
+        <v>392</v>
+      </c>
       <c r="B42" s="32" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="C42" s="32" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
+      <c r="A43" s="7" t="s">
+        <v>393</v>
+      </c>
       <c r="B43" s="32" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
+      <c r="A44" s="7" t="s">
+        <v>394</v>
+      </c>
       <c r="B44" s="1" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
+      <c r="A45" s="7" t="s">
+        <v>395</v>
+      </c>
       <c r="B45" s="1" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
+      <c r="A46" s="7" t="s">
+        <v>396</v>
+      </c>
       <c r="B46" s="1" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
+      <c r="A47" s="7" t="s">
+        <v>397</v>
+      </c>
       <c r="B47" s="1" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
+      <c r="A48" s="7" t="s">
+        <v>398</v>
+      </c>
       <c r="B48" s="14" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
+      <c r="A49" s="7" t="s">
+        <v>399</v>
+      </c>
       <c r="B49" s="14" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="D49" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
+      <c r="A50" s="7" t="s">
+        <v>400</v>
+      </c>
       <c r="B50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>363</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
+      <c r="A51" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="B51" s="1" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
+      <c r="A52" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="B52" s="1" t="s">
-        <v>374</v>
+        <v>435</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
+      <c r="A53" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="B53" s="1" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
+      <c r="A54" s="7" t="s">
+        <v>404</v>
+      </c>
       <c r="B54" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C54" s="14"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="9"/>
+      <c r="A55" s="7" t="s">
+        <v>405</v>
+      </c>
       <c r="B55" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C55" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="C55" s="34" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
+      <c r="A56" s="7" t="s">
+        <v>406</v>
+      </c>
       <c r="B56" s="1" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
+      <c r="A57" s="7" t="s">
+        <v>407</v>
+      </c>
       <c r="B57" s="1" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
+      <c r="A58" s="7" t="s">
+        <v>408</v>
+      </c>
       <c r="B58" s="1" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
+      <c r="A59" s="7" t="s">
+        <v>409</v>
+      </c>
       <c r="B59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
+      <c r="A60" s="7" t="s">
+        <v>410</v>
+      </c>
       <c r="B60" s="1" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
+      <c r="A61" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="B61" s="1" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="9"/>
+      <c r="A62" s="7" t="s">
+        <v>412</v>
+      </c>
       <c r="B62" s="1" t="s">
-        <v>358</v>
+        <v>436</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
+      <c r="A63" s="7" t="s">
+        <v>413</v>
+      </c>
       <c r="B63" s="1" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
+      <c r="A64" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="B64" s="1" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
+      <c r="A65" s="7" t="s">
+        <v>415</v>
+      </c>
       <c r="B65" s="1" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
+      <c r="A66" s="7" t="s">
+        <v>416</v>
+      </c>
       <c r="B66" s="1" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
+      <c r="A67" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="B67" s="1" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
+      <c r="A68" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="B68" s="1" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
+      <c r="A69" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="B69" s="1" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="9"/>
+      <c r="A70" s="7" t="s">
+        <v>420</v>
+      </c>
       <c r="B70" s="1" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="9"/>
+      <c r="A71" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="B71" s="1" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
+      <c r="A72" s="7" t="s">
+        <v>422</v>
+      </c>
       <c r="B72" s="1" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
+      <c r="A73" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="B73" s="1" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
+      <c r="A74" s="7" t="s">
+        <v>424</v>
+      </c>
       <c r="B74" s="1" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="9"/>
+      <c r="A75" s="7" t="s">
+        <v>425</v>
+      </c>
       <c r="B75" s="1" t="s">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="9"/>
+      <c r="A76" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="9"/>
+      <c r="A77" s="7" t="s">
+        <v>427</v>
+      </c>
       <c r="B77" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="9"/>
+      <c r="A78" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="B78" s="1" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="9"/>
+      <c r="A79" s="7" t="s">
+        <v>429</v>
+      </c>
       <c r="B79" s="1" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="9"/>
+      <c r="A80" s="7" t="s">
+        <v>430</v>
+      </c>
       <c r="B80" s="1" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="9"/>
+      <c r="A81" s="7" t="s">
+        <v>432</v>
+      </c>
       <c r="B81" s="1" t="s">
-        <v>28</v>
+        <v>233</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="9"/>
+      <c r="A82" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="B82" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="9"/>
+      <c r="A83" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="B83" s="1" t="s">
         <v>263</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>378</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:C82">
+  <autoFilter ref="B1:C83">
     <sortState ref="B2:C100">
       <sortCondition ref="B1:B100"/>
     </sortState>
@@ -7387,1455 +7735,1573 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:AJ141"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.08203125" customWidth="1"/>
-    <col min="2" max="2" width="39.83203125" customWidth="1"/>
-    <col min="3" max="4" width="41.5" customWidth="1"/>
-    <col min="6" max="6" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="36" width="8.6640625" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>280</v>
+      <c r="C1" s="19" t="s">
+        <v>250</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C2" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D2" s="22"/>
-      <c r="F2" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="25"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="D4" s="22"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="D5" s="22"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C6" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="D6" s="22"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="D7" s="22"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10" s="22"/>
       <c r="D10" s="22"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C11" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="D11" s="22"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="22"/>
       <c r="D16" s="22"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D17" s="22"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="22"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-    </row>
-    <row r="19" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="B19" s="24" t="s">
+      <c r="D20" s="22"/>
+    </row>
+    <row r="21" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
+      <c r="D21" s="25"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="A22" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="28"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="D23" s="22"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C24" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="D24" s="22"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C25" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D25" s="22"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="D26" s="22"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C27" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>228</v>
+      </c>
       <c r="D27" s="22"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D28" s="22"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="D29" s="22"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D30" s="22"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" s="22"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D32" s="22"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D33" s="22"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C34" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D34" s="22"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D35" s="22"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="D36" s="22"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C37" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D37" s="22"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D38" s="22"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="D39" s="22"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="D40" s="22"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D41" s="22"/>
     </row>
     <row r="42" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
+      <c r="A42" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="22"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B43" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="C43" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="28"/>
       <c r="D43" s="28"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="22"/>
       <c r="D44" s="22"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="22"/>
       <c r="D45" s="22"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C46" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="D46" s="22"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C47" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="D47" s="22"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="22"/>
       <c r="D48" s="22"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C49" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="D49" s="22"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C50" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="D50" s="22"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="D51" s="22"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C52" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="D52" s="22"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B53" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="22"/>
       <c r="D53" s="22"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B54" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="22"/>
       <c r="D54" s="22"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B55" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="22"/>
       <c r="D55" s="22"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B56" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="22"/>
       <c r="D56" s="22"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B57" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="22"/>
       <c r="D57" s="22"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B58" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="22"/>
       <c r="D58" s="22"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B59" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="22"/>
       <c r="D59" s="22"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B60" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="22"/>
       <c r="D60" s="22"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C61" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="D61" s="22"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B62" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="22"/>
       <c r="D62" s="22"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="D63" s="22"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C64" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="D64" s="22"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C65" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="D65" s="22"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C66" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="D66" s="22"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C67" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>438</v>
+      </c>
       <c r="D67" s="22"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C68" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="D68" s="22"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C69" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B69" s="22"/>
+      <c r="C69" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D69" s="22"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B70" s="22"/>
+      <c r="C70" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D70" s="22"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B71" s="22"/>
+      <c r="C71" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D71" s="22"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B72" s="22"/>
+      <c r="C72" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="D72" s="22"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C73" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B73" s="22"/>
+      <c r="C73" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="D73" s="22"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C74" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B74" s="22"/>
+      <c r="C74" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="D74" s="22"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C75" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B75" s="22"/>
+      <c r="C75" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="D75" s="22"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B76" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="D76" s="22"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C77" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B77" s="22"/>
+      <c r="C77" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="D77" s="22"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B78" s="22"/>
+      <c r="C78" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="D78" s="22"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B79" s="22"/>
+      <c r="C79" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D79" s="22"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C80" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="B80" s="22"/>
+      <c r="C80" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D80" s="22"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
-    </row>
-    <row r="82" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="B82" s="24" t="s">
+    <row r="81" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" s="25"/>
+      <c r="C81" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
+      <c r="D81" s="25"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B82" s="28"/>
+      <c r="C82" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82" s="28"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="C83" s="28"/>
-      <c r="D83" s="28"/>
+      <c r="A83" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="B83" s="22"/>
+      <c r="C83" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D83" s="22"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C84" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B84" s="22"/>
+      <c r="C84" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="D84" s="22"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C85" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B85" s="22"/>
+      <c r="C85" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D85" s="22"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C86" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B86" s="22"/>
+      <c r="C86" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="D86" s="22"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B87" s="22"/>
+      <c r="C87" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="D87" s="22"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C88" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B88" s="22"/>
+      <c r="C88" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="D88" s="22"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C89" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B89" s="22"/>
+      <c r="C89" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="D89" s="22"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C90" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B90" s="22"/>
+      <c r="C90" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="D90" s="22"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C91" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B91" s="22"/>
+      <c r="C91" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="D91" s="22"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C92" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B92" s="22"/>
+      <c r="C92" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="D92" s="22"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C93" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B93" s="22"/>
+      <c r="C93" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="D93" s="22"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C94" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B94" s="22"/>
+      <c r="C94" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="D94" s="22"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C95" s="22"/>
+        <v>255</v>
+      </c>
+      <c r="B95" s="22"/>
+      <c r="C95" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="D95" s="22"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22"/>
-    </row>
-    <row r="97" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25"/>
+    <row r="96" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B96" s="25"/>
+      <c r="C96" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D96" s="25"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B97" s="28"/>
+      <c r="C97" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D97" s="28"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B98" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C98" s="28"/>
-      <c r="D98" s="28"/>
+      <c r="A98" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="B98" s="22"/>
+      <c r="C98" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D98" s="22"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C99" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B99" s="22"/>
+      <c r="C99" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="D99" s="22"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C100" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B100" s="22"/>
+      <c r="C100" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D100" s="22"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C101" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B101" s="22"/>
+      <c r="C101" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="D101" s="22"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C102" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B102" s="22"/>
+      <c r="C102" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="D102" s="22"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C103" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B103" s="22"/>
+      <c r="C103" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="D103" s="22"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C104" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B104" s="22"/>
+      <c r="C104" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="D104" s="22"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C105" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B105" s="22"/>
+      <c r="C105" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="D105" s="22"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C106" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B106" s="22"/>
+      <c r="C106" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D106" s="22"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B107" s="22"/>
+      <c r="C107" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D107" s="22"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C108" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B108" s="22"/>
+      <c r="C108" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="D108" s="22"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C109" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B109" s="22"/>
+      <c r="C109" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="D109" s="22"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C110" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B110" s="22"/>
+      <c r="C110" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="D110" s="22"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C111" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B111" s="22"/>
+      <c r="C111" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D111" s="22"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B112" s="22"/>
+      <c r="C112" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="D112" s="22"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C113" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B113" s="22"/>
+      <c r="C113" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="D113" s="22"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C114" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B114" s="22"/>
+      <c r="C114" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D114" s="22"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B115" s="22"/>
+      <c r="C115" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="D115" s="22"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C116" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B116" s="22"/>
+      <c r="C116" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="D116" s="22"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C117" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B117" s="22"/>
+      <c r="C117" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="D117" s="22"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C118" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B118" s="22"/>
+      <c r="C118" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="D118" s="22"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C119" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B119" s="22"/>
+      <c r="C119" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="D119" s="22"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C120" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B120" s="22"/>
+      <c r="C120" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="D120" s="22"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C121" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B121" s="22"/>
+      <c r="C121" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="D121" s="22"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C122" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B122" s="22"/>
+      <c r="C122" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="D122" s="22"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C123" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B123" s="22"/>
+      <c r="C123" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="D123" s="22"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C124" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B124" s="22"/>
+      <c r="C124" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="D124" s="22"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C125" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B125" s="22"/>
+      <c r="C125" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="D125" s="22"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C126" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B126" s="22"/>
+      <c r="C126" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="D126" s="22"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C127" s="22"/>
+        <v>256</v>
+      </c>
+      <c r="B127" s="22"/>
+      <c r="C127" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="D127" s="22"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-    </row>
-    <row r="129" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="B129" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25"/>
+    <row r="128" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B128" s="25"/>
+      <c r="C128" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D128" s="25"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" s="28"/>
+      <c r="C129" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129" s="28"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="B130" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="28"/>
-      <c r="D130" s="28"/>
+      <c r="A130" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" s="22"/>
+      <c r="C130" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="22"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C131" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B131" s="22"/>
+      <c r="C131" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D131" s="22"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C132" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B132" s="22"/>
+      <c r="C132" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D132" s="22"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C133" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B133" s="22"/>
+      <c r="C133" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="D133" s="22"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C134" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B134" s="22"/>
+      <c r="C134" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D134" s="22"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B135" s="22"/>
+      <c r="C135" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D135" s="22"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B136" s="22"/>
+      <c r="C136" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="D136" s="22"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C137" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B137" s="22"/>
+      <c r="C137" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="D137" s="22"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C138" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B138" s="22"/>
+      <c r="C138" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="D138" s="22"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C139" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B139" s="22"/>
+      <c r="C139" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="D139" s="22"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C140" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="B140" s="22"/>
+      <c r="C140" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D140" s="22"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C141" s="22"/>
-      <c r="D141" s="22"/>
-    </row>
-    <row r="142" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="B142" s="24" t="s">
+    <row r="141" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B141" s="25"/>
+      <c r="C141" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C142" s="25"/>
-      <c r="D142" s="25"/>
+      <c r="D141" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D142"/>
+  <autoFilter ref="A1:D141"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F245"/>
+  <dimension ref="B1:E188"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.25" customWidth="1"/>
@@ -8844,12 +9310,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8859,17 +9325,17 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -8877,10 +9343,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -8888,10 +9354,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -8899,10 +9365,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -8910,10 +9376,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -8921,10 +9387,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -8935,7 +9401,7 @@
         <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -8943,10 +9409,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -8954,10 +9420,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -8965,10 +9431,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -8979,7 +9445,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -8990,7 +9456,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -9001,7 +9467,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -9012,7 +9478,7 @@
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -9023,7 +9489,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -9031,10 +9497,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -9473,391 +9939,89 @@
     <row r="160" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B160" s="6"/>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="6"/>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="6"/>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="6"/>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="6"/>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="6"/>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="6"/>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="6"/>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="6"/>
-      <c r="F168" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="6"/>
-      <c r="F169" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="6"/>
-      <c r="F170" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="6"/>
-      <c r="F171" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="6"/>
-      <c r="F172" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="6"/>
-      <c r="F173" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="6"/>
-      <c r="F174" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="6"/>
-      <c r="F175" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="6"/>
-      <c r="F176" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="6"/>
-      <c r="F177" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="6"/>
-      <c r="F178" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="6"/>
-      <c r="F179" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="6"/>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="6"/>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="6"/>
-      <c r="F182" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="6"/>
-      <c r="F183" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="6"/>
-      <c r="F184" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="6"/>
-      <c r="F185" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="6"/>
-      <c r="F186" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="6"/>
-      <c r="F187" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="6"/>
-      <c r="F188" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F189" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F190" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F191" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="F192" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="193" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F193" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="194" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F194" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="195" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F195" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="196" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F196" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="197" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F197" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="200" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F200" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="201" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F201" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="202" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F202" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="203" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F203" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="204" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F204" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="205" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F205" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="206" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F206" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="207" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F207" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="208" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F208" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="209" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F209" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="210" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F210" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="211" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F211" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="212" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F212" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="213" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F213" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="214" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F214" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="215" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F215" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="216" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F216" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="217" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F217">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="218" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F218" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="221" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F221" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="222" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F222" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="224" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F224" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="226" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F226" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="228" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F228" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="230" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F230" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="231" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F231" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="232" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F232" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="233" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F233" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="234" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F234" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="235" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F235" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="236" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F236" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="237" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F237" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="238" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F238" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="239" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F239" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="240" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F240" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="241" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F241" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="242" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F242" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="243" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F243" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="244" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F244" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="245" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F245" t="s">
-        <v>209</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9885,12 +10049,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9900,17 +10064,17 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -9921,7 +10085,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -9932,7 +10096,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -9943,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -9951,10 +10115,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -9962,10 +10126,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -9976,7 +10140,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -9984,10 +10148,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -9998,7 +10162,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -10009,7 +10173,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -10020,7 +10184,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -10031,7 +10195,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -10042,7 +10206,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -10053,7 +10217,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -10061,10 +10225,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -10075,7 +10239,7 @@
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -10086,7 +10250,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -10094,10 +10258,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
@@ -10105,10 +10269,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
@@ -10119,7 +10283,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
@@ -10130,7 +10294,7 @@
         <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
@@ -10141,7 +10305,7 @@
         <v>25</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -10152,49 +10316,49 @@
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="E26" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="5"/>
       <c r="E27" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="E28" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="6"/>
       <c r="E29" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="6"/>
       <c r="E30" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="6"/>
       <c r="E31" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="6"/>
       <c r="E32" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
@@ -10697,12 +10861,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10712,7 +10876,7 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
@@ -10722,7 +10886,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -10733,7 +10897,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -10744,7 +10908,7 @@
         <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -10752,10 +10916,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -10763,10 +10927,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -10785,7 +10949,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>88</v>
@@ -10796,10 +10960,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -10807,10 +10971,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -10818,10 +10982,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -10832,7 +10996,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -10843,7 +11007,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -10854,7 +11018,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -10865,7 +11029,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -10876,7 +11040,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -10887,7 +11051,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -10898,7 +11062,7 @@
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -10909,7 +11073,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
@@ -10917,10 +11081,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
@@ -10931,7 +11095,7 @@
         <v>41</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
@@ -10939,10 +11103,10 @@
         <v>21</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
@@ -10950,10 +11114,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -10961,10 +11125,10 @@
         <v>23</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
@@ -10972,10 +11136,10 @@
         <v>24</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
@@ -10983,10 +11147,10 @@
         <v>25</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
@@ -10997,7 +11161,7 @@
         <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
@@ -11008,7 +11172,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
@@ -11019,7 +11183,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
@@ -11030,7 +11194,7 @@
         <v>32</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
@@ -11041,7 +11205,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
@@ -11049,10 +11213,10 @@
         <v>31</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
@@ -11060,10 +11224,10 @@
         <v>32</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
@@ -11071,10 +11235,10 @@
         <v>33</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
@@ -11082,10 +11246,10 @@
         <v>34</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
@@ -11096,7 +11260,7 @@
         <v>51</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
@@ -11107,7 +11271,7 @@
         <v>31</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
@@ -11118,7 +11282,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
@@ -11129,7 +11293,7 @@
         <v>54</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
@@ -11475,12 +11639,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11490,17 +11654,17 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -11508,10 +11672,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -11519,10 +11683,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -11533,7 +11697,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -11541,10 +11705,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -11552,7 +11716,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -11560,7 +11724,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -11568,7 +11732,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -11576,10 +11740,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -11587,7 +11751,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -11595,7 +11759,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -11603,7 +11767,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -11611,7 +11775,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
@@ -11619,7 +11783,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -11627,7 +11791,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -11785,12 +11949,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="38" t="s">
-        <v>230</v>
+      <c r="C1" s="38"/>
+      <c r="E1" s="39" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -11800,7 +11964,7 @@
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="38"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7">
@@ -11810,7 +11974,7 @@
         <v>59</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -11821,7 +11985,7 @@
         <v>60</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -11832,7 +11996,7 @@
         <v>61</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -11843,7 +12007,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -11876,7 +12040,7 @@
         <v>64</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -11887,7 +12051,7 @@
         <v>68</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -11898,7 +12062,7 @@
         <v>69</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -11909,7 +12073,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -11920,7 +12084,7 @@
         <v>70</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -11928,10 +12092,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
@@ -11978,34 +12142,34 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="7">
+      <c r="B20" s="43">
         <v>18</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="16" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="7">
+      <c r="B21" s="43">
         <v>19</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="7">
+      <c r="B22" s="43">
         <v>20</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="16" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="7">
+      <c r="B23" s="43">
         <v>21</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="16" t="s">
         <v>78</v>
       </c>
     </row>
@@ -12014,7 +12178,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -12022,7 +12186,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
@@ -12030,7 +12194,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
@@ -12038,7 +12202,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
@@ -12046,7 +12210,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
@@ -12054,7 +12218,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
@@ -12062,7 +12226,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
@@ -12070,7 +12234,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
@@ -12086,7 +12250,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -12094,7 +12258,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
